--- a/atlas_master.xlsx
+++ b/atlas_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toby/proj/atlas_antarktiki/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B305FDE1-1245-1745-B899-DE52758844CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC23CD4-84B1-2443-816F-BEAB1B18BB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3180" windowWidth="34560" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9764" uniqueCount="2406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9749" uniqueCount="2404">
   <si>
     <t>Unnamed: 0</t>
   </si>
@@ -3883,9 +3883,6 @@
     <t>188</t>
   </si>
   <si>
-    <t>Physical and chemical properties Weddell Sea</t>
-  </si>
-  <si>
     <t>atlas/3_regional/13_southern_ocean/49_atlantic_sector_and_weddell_sea_p_181-189/maps/P_188_VI.tiff</t>
   </si>
   <si>
@@ -4082,9 +4079,6 @@
   </si>
   <si>
     <t>atlas/3_regional/13_southern_ocean/50_indian_sector_and_davis_sea_p_190-207/maps/P_200_VIII_A.tiff</t>
-  </si>
-  <si>
-    <t>Content of Fraction 0.05‚Äì0.01 mm</t>
   </si>
   <si>
     <t>atlas/3_regional/13_southern_ocean/50_indian_sector_and_davis_sea_p_190-207/maps/P_200_VIII_B.tiff</t>
@@ -7601,9 +7595,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U635"/>
+  <dimension ref="A1:U634"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
+    <col min="5" max="5" width="48.1640625" customWidth="1"/>
     <col min="10" max="10" width="59.6640625" customWidth="1"/>
     <col min="12" max="12" width="17.1640625" customWidth="1"/>
     <col min="13" max="13" width="21" customWidth="1"/>
@@ -9558,10 +9554,10 @@
         <v>107</v>
       </c>
       <c r="T34" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="U34" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.2">
@@ -9611,10 +9607,10 @@
         <v>109</v>
       </c>
       <c r="T35" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="U35" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.2">
@@ -9667,10 +9663,10 @@
         <v>112</v>
       </c>
       <c r="T36" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="U36" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.2">
@@ -9723,10 +9719,10 @@
         <v>114</v>
       </c>
       <c r="T37" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="U37" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.2">
@@ -9776,10 +9772,10 @@
         <v>117</v>
       </c>
       <c r="T38" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="U38" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.2">
@@ -9832,10 +9828,10 @@
         <v>119</v>
       </c>
       <c r="T39" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="U39" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.2">
@@ -9888,10 +9884,10 @@
         <v>121</v>
       </c>
       <c r="T40" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="U40" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.2">
@@ -9941,10 +9937,10 @@
         <v>124</v>
       </c>
       <c r="T41" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="U41" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.2">
@@ -9997,10 +9993,10 @@
         <v>126</v>
       </c>
       <c r="T42" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="U42" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.2">
@@ -10103,10 +10099,10 @@
         <v>132</v>
       </c>
       <c r="T44" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="U44" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
@@ -10215,10 +10211,10 @@
         <v>136</v>
       </c>
       <c r="T46" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="U46" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.2">
@@ -10271,10 +10267,10 @@
         <v>139</v>
       </c>
       <c r="T47" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="U47" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.2">
@@ -10327,10 +10323,10 @@
         <v>141</v>
       </c>
       <c r="T48" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="U48" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
@@ -10380,10 +10376,10 @@
         <v>146</v>
       </c>
       <c r="T49" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="U49" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.2">
@@ -10489,10 +10485,10 @@
         <v>151</v>
       </c>
       <c r="T51" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="U51" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
@@ -10542,10 +10538,10 @@
         <v>154</v>
       </c>
       <c r="T52" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="U52" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
@@ -10598,10 +10594,10 @@
         <v>156</v>
       </c>
       <c r="T53" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="U53" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
@@ -10651,10 +10647,10 @@
         <v>163</v>
       </c>
       <c r="T54" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="U54" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.2">
@@ -10707,10 +10703,10 @@
         <v>165</v>
       </c>
       <c r="T55" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="U55" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.2">
@@ -10763,10 +10759,10 @@
         <v>167</v>
       </c>
       <c r="T56" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="U56" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.2">
@@ -10819,10 +10815,10 @@
         <v>169</v>
       </c>
       <c r="T57" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="U57" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.2">
@@ -10872,10 +10868,10 @@
         <v>174</v>
       </c>
       <c r="T58" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="U58" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
@@ -10925,10 +10921,10 @@
         <v>176</v>
       </c>
       <c r="T59" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="U59" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.2">
@@ -11028,10 +11024,10 @@
         <v>184</v>
       </c>
       <c r="T61" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="U61" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.2">
@@ -11078,10 +11074,10 @@
         <v>189</v>
       </c>
       <c r="T62" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="U62" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.2">
@@ -11128,10 +11124,10 @@
         <v>193</v>
       </c>
       <c r="T63" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="U63" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.2">
@@ -11178,10 +11174,10 @@
         <v>198</v>
       </c>
       <c r="T64" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="U64" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.2">
@@ -11228,10 +11224,10 @@
         <v>202</v>
       </c>
       <c r="T65" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="U65" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.2">
@@ -11278,10 +11274,10 @@
         <v>206</v>
       </c>
       <c r="T66" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="U66" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.2">
@@ -11328,10 +11324,10 @@
         <v>210</v>
       </c>
       <c r="T67" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="U67" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.2">
@@ -11378,10 +11374,10 @@
         <v>214</v>
       </c>
       <c r="T68" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="U68" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.2">
@@ -11564,10 +11560,10 @@
         <v>225</v>
       </c>
       <c r="T71" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="U71" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.2">
@@ -11626,10 +11622,10 @@
         <v>227</v>
       </c>
       <c r="T72" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="U72" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.2">
@@ -11688,10 +11684,10 @@
         <v>229</v>
       </c>
       <c r="T73" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="U73" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.2">
@@ -11750,10 +11746,10 @@
         <v>231</v>
       </c>
       <c r="T74" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="U74" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.2">
@@ -11812,10 +11808,10 @@
         <v>233</v>
       </c>
       <c r="T75" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="U75" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.2">
@@ -11874,10 +11870,10 @@
         <v>235</v>
       </c>
       <c r="T76" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="U76" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.2">
@@ -11936,10 +11932,10 @@
         <v>237</v>
       </c>
       <c r="T77" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="U77" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.2">
@@ -11998,10 +11994,10 @@
         <v>239</v>
       </c>
       <c r="T78" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="U78" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.2">
@@ -12184,10 +12180,10 @@
         <v>242</v>
       </c>
       <c r="T81" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="U81" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.2">
@@ -12246,10 +12242,10 @@
         <v>243</v>
       </c>
       <c r="T82" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="U82" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.2">
@@ -12308,10 +12304,10 @@
         <v>244</v>
       </c>
       <c r="T83" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="U83" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.2">
@@ -12370,10 +12366,10 @@
         <v>245</v>
       </c>
       <c r="T84" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="U84" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.2">
@@ -12432,10 +12428,10 @@
         <v>246</v>
       </c>
       <c r="T85" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="U85" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.2">
@@ -12494,10 +12490,10 @@
         <v>247</v>
       </c>
       <c r="T86" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="U86" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.2">
@@ -12556,10 +12552,10 @@
         <v>248</v>
       </c>
       <c r="T87" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="U87" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.2">
@@ -12618,10 +12614,10 @@
         <v>249</v>
       </c>
       <c r="T88" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="U88" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.2">
@@ -12804,10 +12800,10 @@
         <v>252</v>
       </c>
       <c r="T91" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="U91" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.2">
@@ -12866,10 +12862,10 @@
         <v>253</v>
       </c>
       <c r="T92" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="U92" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.2">
@@ -12928,10 +12924,10 @@
         <v>254</v>
       </c>
       <c r="T93" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="U93" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.2">
@@ -12990,10 +12986,10 @@
         <v>255</v>
       </c>
       <c r="T94" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="U94" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.2">
@@ -13052,10 +13048,10 @@
         <v>256</v>
       </c>
       <c r="T95" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="U95" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.2">
@@ -13114,10 +13110,10 @@
         <v>257</v>
       </c>
       <c r="T96" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="U96" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.2">
@@ -13176,10 +13172,10 @@
         <v>258</v>
       </c>
       <c r="T97" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="U97" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.2">
@@ -13238,10 +13234,10 @@
         <v>259</v>
       </c>
       <c r="T98" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="U98" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.2">
@@ -13424,10 +13420,10 @@
         <v>262</v>
       </c>
       <c r="T101" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="U101" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.2">
@@ -13486,10 +13482,10 @@
         <v>263</v>
       </c>
       <c r="T102" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="U102" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.2">
@@ -13548,10 +13544,10 @@
         <v>264</v>
       </c>
       <c r="T103" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="U103" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.2">
@@ -13610,10 +13606,10 @@
         <v>265</v>
       </c>
       <c r="T104" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="U104" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.2">
@@ -13672,10 +13668,10 @@
         <v>266</v>
       </c>
       <c r="T105" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="U105" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.2">
@@ -13734,10 +13730,10 @@
         <v>267</v>
       </c>
       <c r="T106" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="U106" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.2">
@@ -13796,10 +13792,10 @@
         <v>268</v>
       </c>
       <c r="T107" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="U107" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.2">
@@ -13858,10 +13854,10 @@
         <v>269</v>
       </c>
       <c r="T108" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="U108" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.2">
@@ -14720,10 +14716,10 @@
         <v>292</v>
       </c>
       <c r="T122" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="U122" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.2">
@@ -14776,10 +14772,10 @@
         <v>294</v>
       </c>
       <c r="T123" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="U123" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.2">
@@ -14832,10 +14828,10 @@
         <v>297</v>
       </c>
       <c r="T124" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="U124" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.2">
@@ -15000,10 +14996,10 @@
         <v>304</v>
       </c>
       <c r="T127" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="U127" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.2">
@@ -15280,10 +15276,10 @@
         <v>313</v>
       </c>
       <c r="T132" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="U132" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.2">
@@ -15336,10 +15332,10 @@
         <v>315</v>
       </c>
       <c r="T133" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="U133" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.2">
@@ -15392,10 +15388,10 @@
         <v>318</v>
       </c>
       <c r="T134" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="U134" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.2">
@@ -15448,10 +15444,10 @@
         <v>320</v>
       </c>
       <c r="T135" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="U135" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.2">
@@ -15504,10 +15500,10 @@
         <v>323</v>
       </c>
       <c r="T136" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="U136" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.2">
@@ -15560,10 +15556,10 @@
         <v>325</v>
       </c>
       <c r="T137" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="U137" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.2">
@@ -15616,10 +15612,10 @@
         <v>328</v>
       </c>
       <c r="T138" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="U138" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.2">
@@ -15672,10 +15668,10 @@
         <v>330</v>
       </c>
       <c r="T139" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="U139" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.2">
@@ -15728,10 +15724,10 @@
         <v>333</v>
       </c>
       <c r="T140" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="U140" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.2">
@@ -15784,10 +15780,10 @@
         <v>335</v>
       </c>
       <c r="T141" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="U141" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.2">
@@ -15840,10 +15836,10 @@
         <v>337</v>
       </c>
       <c r="T142" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="U142" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.2">
@@ -15896,10 +15892,10 @@
         <v>339</v>
       </c>
       <c r="T143" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="U143" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.2">
@@ -15952,10 +15948,10 @@
         <v>341</v>
       </c>
       <c r="T144" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="U144" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.2">
@@ -16008,10 +16004,10 @@
         <v>343</v>
       </c>
       <c r="T145" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="U145" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.2">
@@ -16064,10 +16060,10 @@
         <v>345</v>
       </c>
       <c r="T146" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="U146" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.2">
@@ -16433,10 +16429,10 @@
         <v>356</v>
       </c>
       <c r="T152" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="U152" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.2">
@@ -16489,10 +16485,10 @@
         <v>361</v>
       </c>
       <c r="T153" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="U153" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.2">
@@ -16548,10 +16544,10 @@
         <v>364</v>
       </c>
       <c r="T154" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="U154" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.2">
@@ -16607,10 +16603,10 @@
         <v>367</v>
       </c>
       <c r="T155" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="U155" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.2">
@@ -17350,10 +17346,10 @@
         <v>402</v>
       </c>
       <c r="T168" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="U168" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.2">
@@ -17406,10 +17402,10 @@
         <v>406</v>
       </c>
       <c r="T169" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="U169" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.2">
@@ -17462,10 +17458,10 @@
         <v>408</v>
       </c>
       <c r="T170" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="U170" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.2">
@@ -17521,10 +17517,10 @@
         <v>411</v>
       </c>
       <c r="T171" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="U171" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.2">
@@ -17580,10 +17576,10 @@
         <v>413</v>
       </c>
       <c r="T172" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="U172" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.2">
@@ -17639,10 +17635,10 @@
         <v>415</v>
       </c>
       <c r="T173" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="U173" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.2">
@@ -17695,10 +17691,10 @@
         <v>419</v>
       </c>
       <c r="T174" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="U174" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.2">
@@ -17754,10 +17750,10 @@
         <v>422</v>
       </c>
       <c r="T175" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="U175" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.2">
@@ -17813,10 +17809,10 @@
         <v>424</v>
       </c>
       <c r="T176" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="U176" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.2">
@@ -17872,10 +17868,10 @@
         <v>426</v>
       </c>
       <c r="T177" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="U177" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.2">
@@ -17928,10 +17924,10 @@
         <v>432</v>
       </c>
       <c r="T178" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="U178" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.2">
@@ -18040,10 +18036,10 @@
         <v>441</v>
       </c>
       <c r="T180" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="U180" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.2">
@@ -18096,10 +18092,10 @@
         <v>444</v>
       </c>
       <c r="T181" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="U181" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.2">
@@ -18152,10 +18148,10 @@
         <v>446</v>
       </c>
       <c r="T182" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="U182" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.2">
@@ -18208,10 +18204,10 @@
         <v>450</v>
       </c>
       <c r="T183" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="U183" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.2">
@@ -18264,10 +18260,10 @@
         <v>453</v>
       </c>
       <c r="T184" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="U184" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.2">
@@ -18320,10 +18316,10 @@
         <v>455</v>
       </c>
       <c r="T185" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="U185" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.2">
@@ -18376,10 +18372,10 @@
         <v>460</v>
       </c>
       <c r="T186" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="U186" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.2">
@@ -18432,10 +18428,10 @@
         <v>463</v>
       </c>
       <c r="T187" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="U187" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.2">
@@ -18488,10 +18484,10 @@
         <v>465</v>
       </c>
       <c r="T188" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="U188" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.2">
@@ -18538,10 +18534,10 @@
         <v>469</v>
       </c>
       <c r="T189" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="U189" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.2">
@@ -18588,10 +18584,10 @@
         <v>472</v>
       </c>
       <c r="T190" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="U190" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.2">
@@ -18638,10 +18634,10 @@
         <v>474</v>
       </c>
       <c r="T191" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="U191" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.2">
@@ -18688,10 +18684,10 @@
         <v>478</v>
       </c>
       <c r="T192" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="U192" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.2">
@@ -18738,10 +18734,10 @@
         <v>481</v>
       </c>
       <c r="T193" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="U193" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.2">
@@ -18791,10 +18787,10 @@
         <v>483</v>
       </c>
       <c r="T194" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="U194" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.2">
@@ -18841,10 +18837,10 @@
         <v>485</v>
       </c>
       <c r="T195" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="U195" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.2">
@@ -18897,10 +18893,10 @@
         <v>491</v>
       </c>
       <c r="T196" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="U196" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.2">
@@ -18953,10 +18949,10 @@
         <v>493</v>
       </c>
       <c r="T197" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="U197" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.2">
@@ -19009,10 +19005,10 @@
         <v>496</v>
       </c>
       <c r="T198" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="U198" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.2">
@@ -19065,10 +19061,10 @@
         <v>498</v>
       </c>
       <c r="T199" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="U199" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.2">
@@ -19121,10 +19117,10 @@
         <v>501</v>
       </c>
       <c r="T200" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="U200" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.2">
@@ -19177,10 +19173,10 @@
         <v>503</v>
       </c>
       <c r="T201" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="U201" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.2">
@@ -19233,10 +19229,10 @@
         <v>507</v>
       </c>
       <c r="T202" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="U202" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.2">
@@ -19289,10 +19285,10 @@
         <v>509</v>
       </c>
       <c r="T203" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="U203" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.2">
@@ -19345,10 +19341,10 @@
         <v>512</v>
       </c>
       <c r="T204" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="U204" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.2">
@@ -19401,10 +19397,10 @@
         <v>514</v>
       </c>
       <c r="T205" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="U205" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.2">
@@ -19457,10 +19453,10 @@
         <v>517</v>
       </c>
       <c r="T206" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="U206" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.2">
@@ -19572,10 +19568,10 @@
         <v>523</v>
       </c>
       <c r="T208" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="U208" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.2">
@@ -19687,10 +19683,10 @@
         <v>527</v>
       </c>
       <c r="T210" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="U210" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.2">
@@ -19746,10 +19742,10 @@
         <v>529</v>
       </c>
       <c r="T211" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="U211" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.2">
@@ -19802,10 +19798,10 @@
         <v>532</v>
       </c>
       <c r="T212" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="U212" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.2">
@@ -19861,10 +19857,10 @@
         <v>534</v>
       </c>
       <c r="T213" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="U213" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.2">
@@ -19917,10 +19913,10 @@
         <v>536</v>
       </c>
       <c r="T214" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="U214" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.2">
@@ -19976,10 +19972,10 @@
         <v>538</v>
       </c>
       <c r="T215" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="U215" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.2">
@@ -20035,10 +20031,10 @@
         <v>540</v>
       </c>
       <c r="T216" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="U216" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.2">
@@ -20091,10 +20087,10 @@
         <v>543</v>
       </c>
       <c r="T217" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="U217" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.2">
@@ -20150,10 +20146,10 @@
         <v>545</v>
       </c>
       <c r="T218" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="U218" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.2">
@@ -20206,10 +20202,10 @@
         <v>547</v>
       </c>
       <c r="T219" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="U219" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.2">
@@ -20265,10 +20261,10 @@
         <v>549</v>
       </c>
       <c r="T220" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="U220" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.2">
@@ -20321,10 +20317,10 @@
         <v>552</v>
       </c>
       <c r="T221" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="U221" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.2">
@@ -20436,10 +20432,10 @@
         <v>555</v>
       </c>
       <c r="T223" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="U223" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.2">
@@ -20495,10 +20491,10 @@
         <v>557</v>
       </c>
       <c r="T224" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="U224" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.2">
@@ -20551,10 +20547,10 @@
         <v>560</v>
       </c>
       <c r="T225" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="U225" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.2">
@@ -20610,10 +20606,10 @@
         <v>562</v>
       </c>
       <c r="T226" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="U226" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.2">
@@ -20666,10 +20662,10 @@
         <v>564</v>
       </c>
       <c r="T227" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="U227" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.2">
@@ -20725,10 +20721,10 @@
         <v>566</v>
       </c>
       <c r="T228" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="U228" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.2">
@@ -20784,10 +20780,10 @@
         <v>567</v>
       </c>
       <c r="T229" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="U229" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.2">
@@ -20840,10 +20836,10 @@
         <v>570</v>
       </c>
       <c r="T230" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="U230" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.2">
@@ -20899,10 +20895,10 @@
         <v>572</v>
       </c>
       <c r="T231" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="U231" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.2">
@@ -20955,10 +20951,10 @@
         <v>574</v>
       </c>
       <c r="T232" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="U232" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.2">
@@ -21014,10 +21010,10 @@
         <v>576</v>
       </c>
       <c r="T233" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="U233" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.2">
@@ -21070,10 +21066,10 @@
         <v>579</v>
       </c>
       <c r="T234" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="U234" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.2">
@@ -21185,10 +21181,10 @@
         <v>582</v>
       </c>
       <c r="T236" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="U236" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.2">
@@ -21300,10 +21296,10 @@
         <v>586</v>
       </c>
       <c r="T238" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="U238" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.2">
@@ -21356,10 +21352,10 @@
         <v>588</v>
       </c>
       <c r="T239" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="U239" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.2">
@@ -21412,10 +21408,10 @@
         <v>592</v>
       </c>
       <c r="T240" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="U240" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="241" spans="1:21" x14ac:dyDescent="0.2">
@@ -21468,10 +21464,10 @@
         <v>594</v>
       </c>
       <c r="T241" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="U241" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="242" spans="1:21" x14ac:dyDescent="0.2">
@@ -21524,10 +21520,10 @@
         <v>596</v>
       </c>
       <c r="T242" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="U242" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="243" spans="1:21" x14ac:dyDescent="0.2">
@@ -21580,10 +21576,10 @@
         <v>598</v>
       </c>
       <c r="T243" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="U243" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="244" spans="1:21" x14ac:dyDescent="0.2">
@@ -21636,10 +21632,10 @@
         <v>600</v>
       </c>
       <c r="T244" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="U244" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="245" spans="1:21" x14ac:dyDescent="0.2">
@@ -21692,10 +21688,10 @@
         <v>602</v>
       </c>
       <c r="T245" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="U245" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="246" spans="1:21" x14ac:dyDescent="0.2">
@@ -21748,10 +21744,10 @@
         <v>606</v>
       </c>
       <c r="T246" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="U246" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="247" spans="1:21" x14ac:dyDescent="0.2">
@@ -21804,10 +21800,10 @@
         <v>608</v>
       </c>
       <c r="T247" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="U247" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="248" spans="1:21" x14ac:dyDescent="0.2">
@@ -21860,10 +21856,10 @@
         <v>610</v>
       </c>
       <c r="T248" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="U248" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="249" spans="1:21" x14ac:dyDescent="0.2">
@@ -21916,10 +21912,10 @@
         <v>613</v>
       </c>
       <c r="T249" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="U249" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="250" spans="1:21" x14ac:dyDescent="0.2">
@@ -21972,10 +21968,10 @@
         <v>615</v>
       </c>
       <c r="T250" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="U250" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="251" spans="1:21" x14ac:dyDescent="0.2">
@@ -22028,10 +22024,10 @@
         <v>617</v>
       </c>
       <c r="T251" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="U251" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="252" spans="1:21" x14ac:dyDescent="0.2">
@@ -22913,10 +22909,10 @@
         <v>636</v>
       </c>
       <c r="T266" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="U266" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="267" spans="1:21" x14ac:dyDescent="0.2">
@@ -22972,10 +22968,10 @@
         <v>638</v>
       </c>
       <c r="T267" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="U267" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="268" spans="1:21" x14ac:dyDescent="0.2">
@@ -23031,10 +23027,10 @@
         <v>641</v>
       </c>
       <c r="T268" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="U268" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="269" spans="1:21" x14ac:dyDescent="0.2">
@@ -23090,10 +23086,10 @@
         <v>643</v>
       </c>
       <c r="T269" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="U269" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="270" spans="1:21" x14ac:dyDescent="0.2">
@@ -23149,10 +23145,10 @@
         <v>646</v>
       </c>
       <c r="T270" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="U270" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="271" spans="1:21" x14ac:dyDescent="0.2">
@@ -23208,10 +23204,10 @@
         <v>648</v>
       </c>
       <c r="T271" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="U271" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="272" spans="1:21" x14ac:dyDescent="0.2">
@@ -23264,10 +23260,10 @@
         <v>655</v>
       </c>
       <c r="T272" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="U272" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="273" spans="1:21" x14ac:dyDescent="0.2">
@@ -23323,10 +23319,10 @@
         <v>658</v>
       </c>
       <c r="T273" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="U273" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="274" spans="1:21" x14ac:dyDescent="0.2">
@@ -23382,10 +23378,10 @@
         <v>660</v>
       </c>
       <c r="T274" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="U274" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="275" spans="1:21" x14ac:dyDescent="0.2">
@@ -23441,10 +23437,10 @@
         <v>662</v>
       </c>
       <c r="T275" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="U275" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="276" spans="1:21" x14ac:dyDescent="0.2">
@@ -23500,10 +23496,10 @@
         <v>664</v>
       </c>
       <c r="T276" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="U276" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="277" spans="1:21" x14ac:dyDescent="0.2">
@@ -23559,10 +23555,10 @@
         <v>666</v>
       </c>
       <c r="T277" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="U277" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="278" spans="1:21" x14ac:dyDescent="0.2">
@@ -23618,10 +23614,10 @@
         <v>668</v>
       </c>
       <c r="T278" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="U278" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="279" spans="1:21" x14ac:dyDescent="0.2">
@@ -23677,10 +23673,10 @@
         <v>671</v>
       </c>
       <c r="T279" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="U279" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="280" spans="1:21" x14ac:dyDescent="0.2">
@@ -24913,10 +24909,10 @@
         <v>698</v>
       </c>
       <c r="T300" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="U300" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="301" spans="1:21" x14ac:dyDescent="0.2">
@@ -25090,10 +25086,10 @@
         <v>703</v>
       </c>
       <c r="T303" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="U303" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="304" spans="1:21" x14ac:dyDescent="0.2">
@@ -25146,10 +25142,10 @@
         <v>705</v>
       </c>
       <c r="T304" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="U304" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="305" spans="1:21" x14ac:dyDescent="0.2">
@@ -25202,10 +25198,10 @@
         <v>707</v>
       </c>
       <c r="T305" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="U305" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="306" spans="1:21" x14ac:dyDescent="0.2">
@@ -25258,10 +25254,10 @@
         <v>713</v>
       </c>
       <c r="T306" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="U306" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="307" spans="1:21" x14ac:dyDescent="0.2">
@@ -25314,10 +25310,10 @@
         <v>717</v>
       </c>
       <c r="T307" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="U307" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="308" spans="1:21" x14ac:dyDescent="0.2">
@@ -25370,10 +25366,10 @@
         <v>719</v>
       </c>
       <c r="T308" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="U308" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="309" spans="1:21" x14ac:dyDescent="0.2">
@@ -25429,10 +25425,10 @@
         <v>721</v>
       </c>
       <c r="T309" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="U309" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="310" spans="1:21" x14ac:dyDescent="0.2">
@@ -25485,10 +25481,10 @@
         <v>724</v>
       </c>
       <c r="T310" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="U310" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="311" spans="1:21" x14ac:dyDescent="0.2">
@@ -25541,10 +25537,10 @@
         <v>726</v>
       </c>
       <c r="T311" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="U311" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="312" spans="1:21" x14ac:dyDescent="0.2">
@@ -25659,10 +25655,10 @@
         <v>729</v>
       </c>
       <c r="T313" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="U313" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="314" spans="1:21" x14ac:dyDescent="0.2">
@@ -25715,10 +25711,10 @@
         <v>733</v>
       </c>
       <c r="T314" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="U314" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="315" spans="1:21" x14ac:dyDescent="0.2">
@@ -25771,10 +25767,10 @@
         <v>735</v>
       </c>
       <c r="T315" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="U315" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="316" spans="1:21" x14ac:dyDescent="0.2">
@@ -25827,10 +25823,10 @@
         <v>738</v>
       </c>
       <c r="T316" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="U316" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="317" spans="1:21" x14ac:dyDescent="0.2">
@@ -25883,10 +25879,10 @@
         <v>740</v>
       </c>
       <c r="T317" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="U317" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="318" spans="1:21" x14ac:dyDescent="0.2">
@@ -25939,10 +25935,10 @@
         <v>743</v>
       </c>
       <c r="T318" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="U318" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="319" spans="1:21" x14ac:dyDescent="0.2">
@@ -25995,10 +25991,10 @@
         <v>745</v>
       </c>
       <c r="T319" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="U319" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="320" spans="1:21" x14ac:dyDescent="0.2">
@@ -26051,10 +26047,10 @@
         <v>749</v>
       </c>
       <c r="T320" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="U320" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="321" spans="1:21" x14ac:dyDescent="0.2">
@@ -26107,10 +26103,10 @@
         <v>751</v>
       </c>
       <c r="T321" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="U321" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="322" spans="1:21" x14ac:dyDescent="0.2">
@@ -26163,10 +26159,10 @@
         <v>754</v>
       </c>
       <c r="T322" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="U322" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="323" spans="1:21" x14ac:dyDescent="0.2">
@@ -26219,10 +26215,10 @@
         <v>756</v>
       </c>
       <c r="T323" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="U323" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="324" spans="1:21" x14ac:dyDescent="0.2">
@@ -26275,10 +26271,10 @@
         <v>759</v>
       </c>
       <c r="T324" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="U324" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="325" spans="1:21" x14ac:dyDescent="0.2">
@@ -26331,10 +26327,10 @@
         <v>761</v>
       </c>
       <c r="T325" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="U325" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="326" spans="1:21" x14ac:dyDescent="0.2">
@@ -26387,10 +26383,10 @@
         <v>765</v>
       </c>
       <c r="T326" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="U326" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="327" spans="1:21" x14ac:dyDescent="0.2">
@@ -26443,10 +26439,10 @@
         <v>769</v>
       </c>
       <c r="T327" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="U327" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="328" spans="1:21" x14ac:dyDescent="0.2">
@@ -26499,10 +26495,10 @@
         <v>771</v>
       </c>
       <c r="T328" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="U328" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="329" spans="1:21" x14ac:dyDescent="0.2">
@@ -26614,10 +26610,10 @@
         <v>776</v>
       </c>
       <c r="T330" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="U330" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="331" spans="1:21" x14ac:dyDescent="0.2">
@@ -26670,10 +26666,10 @@
         <v>778</v>
       </c>
       <c r="T331" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="U331" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="332" spans="1:21" x14ac:dyDescent="0.2">
@@ -26726,10 +26722,10 @@
         <v>780</v>
       </c>
       <c r="T332" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="U332" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="333" spans="1:21" x14ac:dyDescent="0.2">
@@ -26782,10 +26778,10 @@
         <v>782</v>
       </c>
       <c r="T333" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="U333" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="334" spans="1:21" x14ac:dyDescent="0.2">
@@ -26838,10 +26834,10 @@
         <v>785</v>
       </c>
       <c r="T334" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="U334" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="335" spans="1:21" x14ac:dyDescent="0.2">
@@ -26894,10 +26890,10 @@
         <v>787</v>
       </c>
       <c r="T335" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="U335" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="336" spans="1:21" x14ac:dyDescent="0.2">
@@ -26950,10 +26946,10 @@
         <v>790</v>
       </c>
       <c r="T336" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="U336" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="337" spans="1:21" x14ac:dyDescent="0.2">
@@ -27006,10 +27002,10 @@
         <v>792</v>
       </c>
       <c r="T337" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="U337" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="338" spans="1:21" x14ac:dyDescent="0.2">
@@ -27062,10 +27058,10 @@
         <v>795</v>
       </c>
       <c r="T338" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="U338" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="339" spans="1:21" x14ac:dyDescent="0.2">
@@ -27118,10 +27114,10 @@
         <v>798</v>
       </c>
       <c r="T339" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="U339" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="340" spans="1:21" x14ac:dyDescent="0.2">
@@ -27174,10 +27170,10 @@
         <v>802</v>
       </c>
       <c r="T340" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="U340" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="341" spans="1:21" x14ac:dyDescent="0.2">
@@ -27230,10 +27226,10 @@
         <v>805</v>
       </c>
       <c r="T341" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="U341" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="342" spans="1:21" x14ac:dyDescent="0.2">
@@ -27286,10 +27282,10 @@
         <v>809</v>
       </c>
       <c r="T342" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="U342" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="343" spans="1:21" x14ac:dyDescent="0.2">
@@ -27342,10 +27338,10 @@
         <v>812</v>
       </c>
       <c r="T343" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="U343" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="344" spans="1:21" x14ac:dyDescent="0.2">
@@ -27398,10 +27394,10 @@
         <v>816</v>
       </c>
       <c r="T344" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="U344" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="345" spans="1:21" x14ac:dyDescent="0.2">
@@ -27454,10 +27450,10 @@
         <v>819</v>
       </c>
       <c r="T345" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="U345" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="346" spans="1:21" x14ac:dyDescent="0.2">
@@ -27510,10 +27506,10 @@
         <v>823</v>
       </c>
       <c r="T346" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="U346" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="347" spans="1:21" x14ac:dyDescent="0.2">
@@ -27566,10 +27562,10 @@
         <v>826</v>
       </c>
       <c r="T347" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="U347" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="348" spans="1:21" x14ac:dyDescent="0.2">
@@ -27622,10 +27618,10 @@
         <v>830</v>
       </c>
       <c r="T348" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="U348" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="349" spans="1:21" x14ac:dyDescent="0.2">
@@ -27678,10 +27674,10 @@
         <v>833</v>
       </c>
       <c r="T349" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="U349" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="350" spans="1:21" x14ac:dyDescent="0.2">
@@ -27734,10 +27730,10 @@
         <v>836</v>
       </c>
       <c r="T350" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="U350" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="351" spans="1:21" x14ac:dyDescent="0.2">
@@ -27790,10 +27786,10 @@
         <v>839</v>
       </c>
       <c r="T351" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="U351" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="352" spans="1:21" x14ac:dyDescent="0.2">
@@ -27846,10 +27842,10 @@
         <v>842</v>
       </c>
       <c r="T352" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="U352" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="353" spans="1:21" x14ac:dyDescent="0.2">
@@ -28126,10 +28122,10 @@
         <v>852</v>
       </c>
       <c r="T357" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="U357" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="358" spans="1:21" x14ac:dyDescent="0.2">
@@ -28350,10 +28346,10 @@
         <v>861</v>
       </c>
       <c r="T361" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="U361" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="362" spans="1:21" x14ac:dyDescent="0.2">
@@ -28406,10 +28402,10 @@
         <v>863</v>
       </c>
       <c r="T362" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="U362" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="363" spans="1:21" x14ac:dyDescent="0.2">
@@ -28515,10 +28511,10 @@
         <v>867</v>
       </c>
       <c r="T364" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="U364" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="365" spans="1:21" x14ac:dyDescent="0.2">
@@ -28571,10 +28567,10 @@
         <v>870</v>
       </c>
       <c r="T365" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="U365" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="366" spans="1:21" x14ac:dyDescent="0.2">
@@ -28627,10 +28623,10 @@
         <v>872</v>
       </c>
       <c r="T366" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="U366" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="367" spans="1:21" x14ac:dyDescent="0.2">
@@ -28683,10 +28679,10 @@
         <v>878</v>
       </c>
       <c r="T367" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="U367" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="368" spans="1:21" x14ac:dyDescent="0.2">
@@ -28739,10 +28735,10 @@
         <v>880</v>
       </c>
       <c r="T368" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="U368" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="369" spans="1:21" x14ac:dyDescent="0.2">
@@ -28798,10 +28794,10 @@
         <v>883</v>
       </c>
       <c r="T369" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="U369" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="370" spans="1:21" x14ac:dyDescent="0.2">
@@ -28854,10 +28850,10 @@
         <v>886</v>
       </c>
       <c r="T370" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="U370" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="371" spans="1:21" x14ac:dyDescent="0.2">
@@ -28910,10 +28906,10 @@
         <v>888</v>
       </c>
       <c r="T371" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="U371" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="372" spans="1:21" x14ac:dyDescent="0.2">
@@ -28966,10 +28962,10 @@
         <v>891</v>
       </c>
       <c r="T372" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="U372" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="373" spans="1:21" x14ac:dyDescent="0.2">
@@ -29025,10 +29021,10 @@
         <v>893</v>
       </c>
       <c r="T373" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="U373" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="374" spans="1:21" x14ac:dyDescent="0.2">
@@ -29081,10 +29077,10 @@
         <v>895</v>
       </c>
       <c r="T374" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="U374" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="375" spans="1:21" x14ac:dyDescent="0.2">
@@ -29140,10 +29136,10 @@
         <v>897</v>
       </c>
       <c r="T375" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="U375" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="376" spans="1:21" x14ac:dyDescent="0.2">
@@ -29199,10 +29195,10 @@
         <v>899</v>
       </c>
       <c r="T376" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="U376" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="377" spans="1:21" x14ac:dyDescent="0.2">
@@ -29255,10 +29251,10 @@
         <v>903</v>
       </c>
       <c r="T377" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="U377" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="378" spans="1:21" x14ac:dyDescent="0.2">
@@ -29311,10 +29307,10 @@
         <v>905</v>
       </c>
       <c r="T378" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="U378" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="379" spans="1:21" x14ac:dyDescent="0.2">
@@ -29367,10 +29363,10 @@
         <v>908</v>
       </c>
       <c r="T379" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="U379" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="380" spans="1:21" x14ac:dyDescent="0.2">
@@ -29423,10 +29419,10 @@
         <v>910</v>
       </c>
       <c r="T380" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="U380" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="381" spans="1:21" x14ac:dyDescent="0.2">
@@ -29482,10 +29478,10 @@
         <v>912</v>
       </c>
       <c r="T381" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="U381" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="382" spans="1:21" x14ac:dyDescent="0.2">
@@ -29541,10 +29537,10 @@
         <v>914</v>
       </c>
       <c r="T382" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="U382" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="383" spans="1:21" x14ac:dyDescent="0.2">
@@ -29600,10 +29596,10 @@
         <v>916</v>
       </c>
       <c r="T383" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="U383" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="384" spans="1:21" x14ac:dyDescent="0.2">
@@ -29656,10 +29652,10 @@
         <v>920</v>
       </c>
       <c r="T384" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="U384" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="385" spans="1:21" x14ac:dyDescent="0.2">
@@ -29715,10 +29711,10 @@
         <v>922</v>
       </c>
       <c r="T385" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="U385" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="386" spans="1:21" x14ac:dyDescent="0.2">
@@ -29774,10 +29770,10 @@
         <v>924</v>
       </c>
       <c r="T386" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="U386" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="387" spans="1:21" x14ac:dyDescent="0.2">
@@ -29889,10 +29885,10 @@
         <v>927</v>
       </c>
       <c r="T388" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="U388" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="389" spans="1:21" x14ac:dyDescent="0.2">
@@ -29948,10 +29944,10 @@
         <v>929</v>
       </c>
       <c r="T389" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="U389" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="390" spans="1:21" x14ac:dyDescent="0.2">
@@ -30007,10 +30003,10 @@
         <v>931</v>
       </c>
       <c r="T390" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="U390" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="391" spans="1:21" x14ac:dyDescent="0.2">
@@ -30066,10 +30062,10 @@
         <v>933</v>
       </c>
       <c r="T391" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="U391" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="392" spans="1:21" x14ac:dyDescent="0.2">
@@ -30125,10 +30121,10 @@
         <v>935</v>
       </c>
       <c r="T392" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="U392" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="393" spans="1:21" x14ac:dyDescent="0.2">
@@ -30184,10 +30180,10 @@
         <v>937</v>
       </c>
       <c r="T393" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="U393" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="394" spans="1:21" x14ac:dyDescent="0.2">
@@ -30240,10 +30236,10 @@
         <v>944</v>
       </c>
       <c r="T394" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="U394" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="395" spans="1:21" x14ac:dyDescent="0.2">
@@ -30352,10 +30348,10 @@
         <v>949</v>
       </c>
       <c r="T396" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="U396" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="397" spans="1:21" x14ac:dyDescent="0.2">
@@ -30408,10 +30404,10 @@
         <v>956</v>
       </c>
       <c r="T397" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="U397" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="398" spans="1:21" x14ac:dyDescent="0.2">
@@ -30464,10 +30460,10 @@
         <v>962</v>
       </c>
       <c r="T398" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="U398" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="399" spans="1:21" x14ac:dyDescent="0.2">
@@ -30517,10 +30513,10 @@
         <v>965</v>
       </c>
       <c r="T399" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="U399" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="400" spans="1:21" x14ac:dyDescent="0.2">
@@ -30570,10 +30566,10 @@
         <v>968</v>
       </c>
       <c r="T400" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="U400" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="401" spans="1:21" x14ac:dyDescent="0.2">
@@ -30602,7 +30598,7 @@
         <v>40</v>
       </c>
       <c r="I401" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="K401" t="s">
         <v>967</v>
@@ -30623,10 +30619,10 @@
         <v>969</v>
       </c>
       <c r="T401" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="U401" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="402" spans="1:21" x14ac:dyDescent="0.2">
@@ -30673,10 +30669,10 @@
         <v>972</v>
       </c>
       <c r="T402" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="U402" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="403" spans="1:21" x14ac:dyDescent="0.2">
@@ -30705,7 +30701,7 @@
         <v>34</v>
       </c>
       <c r="I403" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="K403" t="s">
         <v>973</v>
@@ -30732,10 +30728,10 @@
         <v>976</v>
       </c>
       <c r="T403" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="U403" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="404" spans="1:21" x14ac:dyDescent="0.2">
@@ -30847,10 +30843,10 @@
         <v>980</v>
       </c>
       <c r="T405" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="U405" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="406" spans="1:21" x14ac:dyDescent="0.2">
@@ -30906,10 +30902,10 @@
         <v>983</v>
       </c>
       <c r="T406" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="U406" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="407" spans="1:21" x14ac:dyDescent="0.2">
@@ -30938,7 +30934,7 @@
         <v>38</v>
       </c>
       <c r="I407" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="K407" t="s">
         <v>657</v>
@@ -30965,10 +30961,10 @@
         <v>984</v>
       </c>
       <c r="T407" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="U407" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="408" spans="1:21" x14ac:dyDescent="0.2">
@@ -31015,10 +31011,10 @@
         <v>988</v>
       </c>
       <c r="T408" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="U408" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="409" spans="1:21" x14ac:dyDescent="0.2">
@@ -31068,10 +31064,10 @@
         <v>991</v>
       </c>
       <c r="T409" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="U409" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="410" spans="1:21" x14ac:dyDescent="0.2">
@@ -31121,10 +31117,10 @@
         <v>993</v>
       </c>
       <c r="T410" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="U410" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="411" spans="1:21" x14ac:dyDescent="0.2">
@@ -31171,10 +31167,10 @@
         <v>996</v>
       </c>
       <c r="T411" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="U411" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="412" spans="1:21" x14ac:dyDescent="0.2">
@@ -31224,10 +31220,10 @@
         <v>998</v>
       </c>
       <c r="T412" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="U412" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="413" spans="1:21" x14ac:dyDescent="0.2">
@@ -31277,10 +31273,10 @@
         <v>1001</v>
       </c>
       <c r="T413" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="U413" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="414" spans="1:21" x14ac:dyDescent="0.2">
@@ -31333,10 +31329,10 @@
         <v>1005</v>
       </c>
       <c r="T414" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="U414" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="415" spans="1:21" x14ac:dyDescent="0.2">
@@ -31392,10 +31388,10 @@
         <v>1009</v>
       </c>
       <c r="T415" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="U415" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="416" spans="1:21" x14ac:dyDescent="0.2">
@@ -31451,10 +31447,10 @@
         <v>1012</v>
       </c>
       <c r="T416" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="U416" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="417" spans="1:21" x14ac:dyDescent="0.2">
@@ -31507,10 +31503,10 @@
         <v>1015</v>
       </c>
       <c r="T417" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="U417" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="418" spans="1:21" x14ac:dyDescent="0.2">
@@ -31622,10 +31618,10 @@
         <v>1019</v>
       </c>
       <c r="T419" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="U419" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="420" spans="1:21" x14ac:dyDescent="0.2">
@@ -31678,10 +31674,10 @@
         <v>1022</v>
       </c>
       <c r="T420" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="U420" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="421" spans="1:21" x14ac:dyDescent="0.2">
@@ -31734,10 +31730,10 @@
         <v>1026</v>
       </c>
       <c r="T421" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="U421" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="422" spans="1:21" x14ac:dyDescent="0.2">
@@ -31952,10 +31948,10 @@
         <v>1032</v>
       </c>
       <c r="T425" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="U425" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="426" spans="1:21" x14ac:dyDescent="0.2">
@@ -32011,10 +32007,10 @@
         <v>1035</v>
       </c>
       <c r="T426" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="U426" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="427" spans="1:21" x14ac:dyDescent="0.2">
@@ -32067,10 +32063,10 @@
         <v>1038</v>
       </c>
       <c r="T427" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="U427" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="428" spans="1:21" x14ac:dyDescent="0.2">
@@ -32123,10 +32119,10 @@
         <v>1040</v>
       </c>
       <c r="T428" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="U428" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="429" spans="1:21" x14ac:dyDescent="0.2">
@@ -32179,10 +32175,10 @@
         <v>1043</v>
       </c>
       <c r="T429" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="U429" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="430" spans="1:21" x14ac:dyDescent="0.2">
@@ -32294,10 +32290,10 @@
         <v>1046</v>
       </c>
       <c r="T431" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="U431" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="432" spans="1:21" x14ac:dyDescent="0.2">
@@ -32406,10 +32402,10 @@
         <v>1050</v>
       </c>
       <c r="T433" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="U433" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="434" spans="1:21" x14ac:dyDescent="0.2">
@@ -32462,10 +32458,10 @@
         <v>1052</v>
       </c>
       <c r="T434" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="U434" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="435" spans="1:21" x14ac:dyDescent="0.2">
@@ -32571,10 +32567,10 @@
         <v>1056</v>
       </c>
       <c r="T436" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="U436" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="437" spans="1:21" x14ac:dyDescent="0.2">
@@ -32627,10 +32623,10 @@
         <v>1058</v>
       </c>
       <c r="T437" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="U437" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="438" spans="1:21" x14ac:dyDescent="0.2">
@@ -32742,10 +32738,10 @@
         <v>1065</v>
       </c>
       <c r="T439" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="U439" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="440" spans="1:21" x14ac:dyDescent="0.2">
@@ -32801,10 +32797,10 @@
         <v>1067</v>
       </c>
       <c r="T440" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="U440" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="441" spans="1:21" x14ac:dyDescent="0.2">
@@ -32907,10 +32903,10 @@
         <v>1071</v>
       </c>
       <c r="T442" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="U442" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="443" spans="1:21" x14ac:dyDescent="0.2">
@@ -33078,10 +33074,10 @@
         <v>1075</v>
       </c>
       <c r="T445" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="U445" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="446" spans="1:21" x14ac:dyDescent="0.2">
@@ -33134,10 +33130,10 @@
         <v>1080</v>
       </c>
       <c r="T446" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="U446" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="447" spans="1:21" x14ac:dyDescent="0.2">
@@ -33296,10 +33292,10 @@
         <v>1085</v>
       </c>
       <c r="T449" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="U449" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="450" spans="1:21" x14ac:dyDescent="0.2">
@@ -33352,10 +33348,10 @@
         <v>1088</v>
       </c>
       <c r="T450" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="U450" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="451" spans="1:21" x14ac:dyDescent="0.2">
@@ -33408,10 +33404,10 @@
         <v>1090</v>
       </c>
       <c r="T451" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="U451" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="452" spans="1:21" x14ac:dyDescent="0.2">
@@ -33467,10 +33463,10 @@
         <v>1093</v>
       </c>
       <c r="T452" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="U452" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="453" spans="1:21" x14ac:dyDescent="0.2">
@@ -33523,10 +33519,10 @@
         <v>1096</v>
       </c>
       <c r="T453" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="U453" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="454" spans="1:21" x14ac:dyDescent="0.2">
@@ -33579,10 +33575,10 @@
         <v>1098</v>
       </c>
       <c r="T454" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="U454" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="455" spans="1:21" x14ac:dyDescent="0.2">
@@ -33694,10 +33690,10 @@
         <v>1100</v>
       </c>
       <c r="T456" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="U456" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="457" spans="1:21" x14ac:dyDescent="0.2">
@@ -33868,10 +33864,10 @@
         <v>1104</v>
       </c>
       <c r="T459" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="U459" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="460" spans="1:21" x14ac:dyDescent="0.2">
@@ -33924,10 +33920,10 @@
         <v>1105</v>
       </c>
       <c r="T460" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="U460" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="461" spans="1:21" x14ac:dyDescent="0.2">
@@ -33980,10 +33976,10 @@
         <v>1108</v>
       </c>
       <c r="T461" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="U461" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="462" spans="1:21" x14ac:dyDescent="0.2">
@@ -34036,10 +34032,10 @@
         <v>1109</v>
       </c>
       <c r="T462" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="U462" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="463" spans="1:21" x14ac:dyDescent="0.2">
@@ -34207,10 +34203,10 @@
         <v>1112</v>
       </c>
       <c r="T465" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="U465" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="466" spans="1:21" x14ac:dyDescent="0.2">
@@ -34263,10 +34259,10 @@
         <v>1113</v>
       </c>
       <c r="T466" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="U466" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="467" spans="1:21" x14ac:dyDescent="0.2">
@@ -34319,10 +34315,10 @@
         <v>1116</v>
       </c>
       <c r="T467" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="U467" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="468" spans="1:21" x14ac:dyDescent="0.2">
@@ -34378,10 +34374,10 @@
         <v>1118</v>
       </c>
       <c r="T468" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="U468" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="469" spans="1:21" x14ac:dyDescent="0.2">
@@ -34484,10 +34480,10 @@
         <v>1121</v>
       </c>
       <c r="T470" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="U470" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="471" spans="1:21" x14ac:dyDescent="0.2">
@@ -34540,10 +34536,10 @@
         <v>1124</v>
       </c>
       <c r="T471" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="U471" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="472" spans="1:21" x14ac:dyDescent="0.2">
@@ -34596,10 +34592,10 @@
         <v>1127</v>
       </c>
       <c r="T472" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="U472" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="473" spans="1:21" x14ac:dyDescent="0.2">
@@ -34655,10 +34651,10 @@
         <v>1129</v>
       </c>
       <c r="T473" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="U473" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="474" spans="1:21" x14ac:dyDescent="0.2">
@@ -34711,10 +34707,10 @@
         <v>1133</v>
       </c>
       <c r="T474" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="U474" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="475" spans="1:21" x14ac:dyDescent="0.2">
@@ -34770,10 +34766,10 @@
         <v>1135</v>
       </c>
       <c r="T475" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="U475" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="476" spans="1:21" x14ac:dyDescent="0.2">
@@ -34829,10 +34825,10 @@
         <v>1137</v>
       </c>
       <c r="T476" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="U476" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="477" spans="1:21" x14ac:dyDescent="0.2">
@@ -35026,10 +35022,10 @@
         <v>1142</v>
       </c>
       <c r="T480" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="U480" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="481" spans="1:21" x14ac:dyDescent="0.2">
@@ -35082,10 +35078,10 @@
         <v>1146</v>
       </c>
       <c r="T481" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="U481" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="482" spans="1:21" x14ac:dyDescent="0.2">
@@ -35141,10 +35137,10 @@
         <v>1149</v>
       </c>
       <c r="T482" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="U482" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="483" spans="1:21" x14ac:dyDescent="0.2">
@@ -35200,10 +35196,10 @@
         <v>1151</v>
       </c>
       <c r="T483" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="U483" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="484" spans="1:21" x14ac:dyDescent="0.2">
@@ -35315,10 +35311,10 @@
         <v>1155</v>
       </c>
       <c r="T485" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="U485" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="486" spans="1:21" x14ac:dyDescent="0.2">
@@ -35374,10 +35370,10 @@
         <v>1157</v>
       </c>
       <c r="T486" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="U486" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="487" spans="1:21" x14ac:dyDescent="0.2">
@@ -35433,10 +35429,10 @@
         <v>1159</v>
       </c>
       <c r="T487" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="U487" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="488" spans="1:21" x14ac:dyDescent="0.2">
@@ -35530,10 +35526,10 @@
         <v>1165</v>
       </c>
       <c r="T489" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="U489" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="490" spans="1:21" x14ac:dyDescent="0.2">
@@ -35583,10 +35579,10 @@
         <v>1168</v>
       </c>
       <c r="T490" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="U490" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="491" spans="1:21" x14ac:dyDescent="0.2">
@@ -35633,10 +35629,10 @@
         <v>1170</v>
       </c>
       <c r="T491" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="U491" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="492" spans="1:21" x14ac:dyDescent="0.2">
@@ -35683,10 +35679,10 @@
         <v>1173</v>
       </c>
       <c r="T492" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="U492" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="493" spans="1:21" x14ac:dyDescent="0.2">
@@ -35736,10 +35732,10 @@
         <v>1175</v>
       </c>
       <c r="T493" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="U493" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="494" spans="1:21" x14ac:dyDescent="0.2">
@@ -35786,10 +35782,10 @@
         <v>1178</v>
       </c>
       <c r="T494" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="U494" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="495" spans="1:21" x14ac:dyDescent="0.2">
@@ -35836,10 +35832,10 @@
         <v>1180</v>
       </c>
       <c r="T495" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="U495" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="496" spans="1:21" x14ac:dyDescent="0.2">
@@ -35886,10 +35882,10 @@
         <v>1182</v>
       </c>
       <c r="T496" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="U496" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="497" spans="1:21" x14ac:dyDescent="0.2">
@@ -35989,10 +35985,10 @@
         <v>1185</v>
       </c>
       <c r="T498" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="U498" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="499" spans="1:21" x14ac:dyDescent="0.2">
@@ -36039,10 +36035,10 @@
         <v>1187</v>
       </c>
       <c r="T499" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="U499" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="500" spans="1:21" x14ac:dyDescent="0.2">
@@ -36089,10 +36085,10 @@
         <v>1189</v>
       </c>
       <c r="T500" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="U500" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="501" spans="1:21" x14ac:dyDescent="0.2">
@@ -36139,10 +36135,10 @@
         <v>1195</v>
       </c>
       <c r="T501" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="U501" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="502" spans="1:21" x14ac:dyDescent="0.2">
@@ -36192,10 +36188,10 @@
         <v>1197</v>
       </c>
       <c r="T502" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="U502" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="503" spans="1:21" x14ac:dyDescent="0.2">
@@ -36289,10 +36285,10 @@
         <v>1201</v>
       </c>
       <c r="T504" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="U504" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="505" spans="1:21" x14ac:dyDescent="0.2">
@@ -36339,10 +36335,10 @@
         <v>1205</v>
       </c>
       <c r="T505" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="U505" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="506" spans="1:21" x14ac:dyDescent="0.2">
@@ -36392,10 +36388,10 @@
         <v>1207</v>
       </c>
       <c r="T506" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="U506" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="507" spans="1:21" x14ac:dyDescent="0.2">
@@ -36445,10 +36441,10 @@
         <v>1210</v>
       </c>
       <c r="T507" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="U507" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="508" spans="1:21" x14ac:dyDescent="0.2">
@@ -36495,10 +36491,10 @@
         <v>1212</v>
       </c>
       <c r="T508" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="U508" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="509" spans="1:21" x14ac:dyDescent="0.2">
@@ -36545,10 +36541,10 @@
         <v>1215</v>
       </c>
       <c r="T509" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="U509" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="510" spans="1:21" x14ac:dyDescent="0.2">
@@ -36595,10 +36591,10 @@
         <v>1218</v>
       </c>
       <c r="T510" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="U510" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="511" spans="1:21" x14ac:dyDescent="0.2">
@@ -36648,10 +36644,10 @@
         <v>1220</v>
       </c>
       <c r="T511" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="U511" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="512" spans="1:21" x14ac:dyDescent="0.2">
@@ -36745,10 +36741,10 @@
         <v>1224</v>
       </c>
       <c r="T513" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="U513" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="514" spans="1:21" x14ac:dyDescent="0.2">
@@ -36798,10 +36794,10 @@
         <v>1226</v>
       </c>
       <c r="T514" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="U514" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="515" spans="1:21" x14ac:dyDescent="0.2">
@@ -36851,10 +36847,10 @@
         <v>1228</v>
       </c>
       <c r="T515" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="U515" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="516" spans="1:21" x14ac:dyDescent="0.2">
@@ -36904,10 +36900,10 @@
         <v>1230</v>
       </c>
       <c r="T516" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="U516" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="517" spans="1:21" x14ac:dyDescent="0.2">
@@ -37048,10 +37044,10 @@
         <v>1236</v>
       </c>
       <c r="T519" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="U519" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="520" spans="1:21" x14ac:dyDescent="0.2">
@@ -37101,10 +37097,10 @@
         <v>1238</v>
       </c>
       <c r="T520" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="U520" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="521" spans="1:21" x14ac:dyDescent="0.2">
@@ -37151,10 +37147,10 @@
         <v>1240</v>
       </c>
       <c r="T521" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="U521" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="522" spans="1:21" x14ac:dyDescent="0.2">
@@ -37201,10 +37197,10 @@
         <v>1242</v>
       </c>
       <c r="T522" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="U522" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="523" spans="1:21" x14ac:dyDescent="0.2">
@@ -37251,10 +37247,10 @@
         <v>1246</v>
       </c>
       <c r="T523" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="U523" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="524" spans="1:21" x14ac:dyDescent="0.2">
@@ -37304,10 +37300,10 @@
         <v>1248</v>
       </c>
       <c r="T524" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="U524" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="525" spans="1:21" x14ac:dyDescent="0.2">
@@ -37354,10 +37350,10 @@
         <v>1250</v>
       </c>
       <c r="T525" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="U525" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="526" spans="1:21" x14ac:dyDescent="0.2">
@@ -37404,10 +37400,10 @@
         <v>1252</v>
       </c>
       <c r="T526" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="U526" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="527" spans="1:21" x14ac:dyDescent="0.2">
@@ -37454,10 +37450,10 @@
         <v>1255</v>
       </c>
       <c r="T527" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="U527" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="528" spans="1:21" x14ac:dyDescent="0.2">
@@ -37504,10 +37500,10 @@
         <v>1257</v>
       </c>
       <c r="T528" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="U528" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="529" spans="1:21" x14ac:dyDescent="0.2">
@@ -37554,10 +37550,10 @@
         <v>1259</v>
       </c>
       <c r="T529" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="U529" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="530" spans="1:21" x14ac:dyDescent="0.2">
@@ -37607,10 +37603,10 @@
         <v>1261</v>
       </c>
       <c r="T530" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="U530" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="531" spans="1:21" x14ac:dyDescent="0.2">
@@ -37657,10 +37653,10 @@
         <v>1263</v>
       </c>
       <c r="T531" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="U531" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="532" spans="1:21" x14ac:dyDescent="0.2">
@@ -37707,10 +37703,10 @@
         <v>1265</v>
       </c>
       <c r="T532" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="U532" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="533" spans="1:21" x14ac:dyDescent="0.2">
@@ -37766,10 +37762,10 @@
         <v>1271</v>
       </c>
       <c r="T533" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="U533" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="534" spans="1:21" x14ac:dyDescent="0.2">
@@ -37881,10 +37877,10 @@
         <v>1277</v>
       </c>
       <c r="T535" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="U535" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="536" spans="1:21" x14ac:dyDescent="0.2">
@@ -37940,10 +37936,10 @@
         <v>1280</v>
       </c>
       <c r="T536" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="U536" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="537" spans="1:21" x14ac:dyDescent="0.2">
@@ -37999,10 +37995,10 @@
         <v>1283</v>
       </c>
       <c r="T537" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="U537" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="538" spans="1:21" x14ac:dyDescent="0.2">
@@ -38055,18 +38051,18 @@
         <v>1285</v>
       </c>
       <c r="T538" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="U538" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="539" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B539">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C539" t="s">
         <v>950</v>
@@ -38081,13 +38077,13 @@
         <v>1286</v>
       </c>
       <c r="G539" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="I539" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="K539" t="s">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="L539" t="s">
         <v>712</v>
@@ -38111,7 +38107,7 @@
         <v>9354</v>
       </c>
       <c r="S539" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="T539" t="s">
         <v>2231</v>
@@ -38122,10 +38118,10 @@
     </row>
     <row r="540" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B540">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C540" t="s">
         <v>950</v>
@@ -38140,10 +38136,10 @@
         <v>1286</v>
       </c>
       <c r="G540" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="I540" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="K540" t="s">
         <v>111</v>
@@ -38170,7 +38166,7 @@
         <v>9354</v>
       </c>
       <c r="S540" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="T540" t="s">
         <v>2233</v>
@@ -38181,10 +38177,10 @@
     </row>
     <row r="541" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B541">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C541" t="s">
         <v>950</v>
@@ -38199,10 +38195,10 @@
         <v>1286</v>
       </c>
       <c r="G541" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="I541" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="K541" t="s">
         <v>111</v>
@@ -38229,7 +38225,7 @@
         <v>9354</v>
       </c>
       <c r="S541" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="T541" t="s">
         <v>2235</v>
@@ -38240,10 +38236,10 @@
     </row>
     <row r="542" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B542">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C542" t="s">
         <v>950</v>
@@ -38258,10 +38254,10 @@
         <v>1286</v>
       </c>
       <c r="G542" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="I542" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="K542" t="s">
         <v>111</v>
@@ -38288,21 +38284,21 @@
         <v>9354</v>
       </c>
       <c r="S542" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
       <c r="T542" t="s">
-        <v>2237</v>
+        <v>2229</v>
       </c>
       <c r="U542" t="s">
-        <v>2238</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="543" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B543">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C543" t="s">
         <v>950</v>
@@ -38317,7 +38313,7 @@
         <v>1286</v>
       </c>
       <c r="G543" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I543" t="s">
         <v>1295</v>
@@ -38347,21 +38343,21 @@
         <v>9354</v>
       </c>
       <c r="S543" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="T543" t="s">
-        <v>2231</v>
+        <v>2237</v>
       </c>
       <c r="U543" t="s">
-        <v>2232</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="544" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B544">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C544" t="s">
         <v>950</v>
@@ -38376,10 +38372,10 @@
         <v>1286</v>
       </c>
       <c r="G544" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I544" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="K544" t="s">
         <v>111</v>
@@ -38406,7 +38402,7 @@
         <v>9354</v>
       </c>
       <c r="S544" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="T544" t="s">
         <v>2239</v>
@@ -38417,10 +38413,10 @@
     </row>
     <row r="545" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B545">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C545" t="s">
         <v>950</v>
@@ -38435,10 +38431,10 @@
         <v>1286</v>
       </c>
       <c r="G545" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I545" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="K545" t="s">
         <v>111</v>
@@ -38465,7 +38461,7 @@
         <v>9354</v>
       </c>
       <c r="S545" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="T545" t="s">
         <v>2241</v>
@@ -38476,10 +38472,10 @@
     </row>
     <row r="546" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B546">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C546" t="s">
         <v>950</v>
@@ -38494,10 +38490,10 @@
         <v>1286</v>
       </c>
       <c r="G546" t="s">
-        <v>152</v>
+        <v>796</v>
       </c>
       <c r="I546" t="s">
-        <v>1300</v>
+        <v>715</v>
       </c>
       <c r="K546" t="s">
         <v>111</v>
@@ -38535,10 +38531,10 @@
     </row>
     <row r="547" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B547">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C547" t="s">
         <v>950</v>
@@ -38550,16 +38546,16 @@
         <v>1267</v>
       </c>
       <c r="F547" t="s">
-        <v>1286</v>
+        <v>1302</v>
       </c>
       <c r="G547" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="I547" t="s">
-        <v>715</v>
+        <v>1303</v>
       </c>
       <c r="K547" t="s">
-        <v>111</v>
+        <v>955</v>
       </c>
       <c r="L547" t="s">
         <v>712</v>
@@ -38568,10 +38564,10 @@
         <v>712</v>
       </c>
       <c r="N547">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O547" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P547" t="s">
         <v>30</v>
@@ -38579,25 +38575,22 @@
       <c r="Q547" t="s">
         <v>30</v>
       </c>
-      <c r="R547">
-        <v>9354</v>
-      </c>
       <c r="S547" t="s">
-        <v>1302</v>
+        <v>30</v>
       </c>
       <c r="T547" t="s">
-        <v>2245</v>
+        <v>30</v>
       </c>
       <c r="U547" t="s">
-        <v>2246</v>
+        <v>30</v>
       </c>
     </row>
     <row r="548" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B548">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C548" t="s">
         <v>950</v>
@@ -38609,16 +38602,19 @@
         <v>1267</v>
       </c>
       <c r="F548" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="G548" t="s">
         <v>800</v>
       </c>
+      <c r="H548" t="s">
+        <v>1304</v>
+      </c>
       <c r="I548" t="s">
-        <v>1304</v>
+        <v>775</v>
       </c>
       <c r="K548" t="s">
-        <v>955</v>
+        <v>105</v>
       </c>
       <c r="L548" t="s">
         <v>712</v>
@@ -38630,7 +38626,7 @@
         <v>270</v>
       </c>
       <c r="O548" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P548" t="s">
         <v>30</v>
@@ -38638,46 +38634,46 @@
       <c r="Q548" t="s">
         <v>30</v>
       </c>
+      <c r="R548">
+        <v>9354</v>
+      </c>
       <c r="S548" t="s">
-        <v>30</v>
+        <v>1305</v>
       </c>
       <c r="T548" t="s">
-        <v>30</v>
+        <v>2245</v>
       </c>
       <c r="U548" t="s">
-        <v>30</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="549" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B549">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C549" t="s">
         <v>950</v>
       </c>
       <c r="D549" t="s">
-        <v>1266</v>
+        <v>1306</v>
       </c>
       <c r="E549" t="s">
-        <v>1267</v>
+        <v>1307</v>
       </c>
       <c r="F549" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="G549" t="s">
-        <v>800</v>
-      </c>
-      <c r="H549" t="s">
-        <v>1305</v>
+        <v>31</v>
       </c>
       <c r="I549" t="s">
-        <v>775</v>
+        <v>1309</v>
       </c>
       <c r="K549" t="s">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="L549" t="s">
         <v>712</v>
@@ -38685,11 +38681,11 @@
       <c r="M549" t="s">
         <v>712</v>
       </c>
-      <c r="N549">
-        <v>270</v>
+      <c r="N549" t="s">
+        <v>1310</v>
       </c>
       <c r="O549" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P549" t="s">
         <v>30</v>
@@ -38701,7 +38697,7 @@
         <v>9354</v>
       </c>
       <c r="S549" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="T549" t="s">
         <v>2247</v>
@@ -38712,31 +38708,31 @@
     </row>
     <row r="550" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B550">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C550" t="s">
         <v>950</v>
       </c>
       <c r="D550" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E550" t="s">
         <v>1307</v>
       </c>
-      <c r="E550" t="s">
-        <v>1308</v>
-      </c>
       <c r="F550" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="G550" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I550" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="K550" t="s">
-        <v>196</v>
+        <v>955</v>
       </c>
       <c r="L550" t="s">
         <v>712</v>
@@ -38744,8 +38740,8 @@
       <c r="M550" t="s">
         <v>712</v>
       </c>
-      <c r="N550" t="s">
-        <v>1311</v>
+      <c r="N550">
+        <v>275</v>
       </c>
       <c r="O550" t="s">
         <v>30</v>
@@ -38756,46 +38752,43 @@
       <c r="Q550" t="s">
         <v>30</v>
       </c>
-      <c r="R550">
-        <v>9354</v>
-      </c>
       <c r="S550" t="s">
-        <v>1312</v>
+        <v>30</v>
       </c>
       <c r="T550" t="s">
-        <v>2249</v>
+        <v>30</v>
       </c>
       <c r="U550" t="s">
-        <v>2250</v>
+        <v>30</v>
       </c>
     </row>
     <row r="551" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B551">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C551" t="s">
         <v>950</v>
       </c>
       <c r="D551" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E551" t="s">
         <v>1307</v>
       </c>
-      <c r="E551" t="s">
-        <v>1308</v>
-      </c>
       <c r="F551" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="G551" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I551" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="K551" t="s">
-        <v>955</v>
+        <v>111</v>
       </c>
       <c r="L551" t="s">
         <v>712</v>
@@ -38803,8 +38796,8 @@
       <c r="M551" t="s">
         <v>712</v>
       </c>
-      <c r="N551">
-        <v>275</v>
+      <c r="N551" t="s">
+        <v>1316</v>
       </c>
       <c r="O551" t="s">
         <v>30</v>
@@ -38815,43 +38808,52 @@
       <c r="Q551" t="s">
         <v>30</v>
       </c>
+      <c r="R551">
+        <v>9354</v>
+      </c>
       <c r="S551" t="s">
-        <v>30</v>
+        <v>1317</v>
       </c>
       <c r="T551" t="s">
-        <v>30</v>
+        <v>2249</v>
       </c>
       <c r="U551" t="s">
-        <v>30</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="552" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B552">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C552" t="s">
         <v>950</v>
       </c>
       <c r="D552" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E552" t="s">
         <v>1307</v>
       </c>
-      <c r="E552" t="s">
-        <v>1308</v>
-      </c>
       <c r="F552" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="G552" t="s">
-        <v>59</v>
+        <v>122</v>
+      </c>
+      <c r="H552" t="s">
+        <v>34</v>
       </c>
       <c r="I552" t="s">
-        <v>1316</v>
+        <v>1319</v>
+      </c>
+      <c r="J552" t="s">
+        <v>1320</v>
       </c>
       <c r="K552" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L552" t="s">
         <v>712</v>
@@ -38859,11 +38861,11 @@
       <c r="M552" t="s">
         <v>712</v>
       </c>
-      <c r="N552" t="s">
-        <v>1317</v>
+      <c r="N552">
+        <v>280</v>
       </c>
       <c r="O552" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P552" t="s">
         <v>30</v>
@@ -38875,7 +38877,7 @@
         <v>9354</v>
       </c>
       <c r="S552" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="T552" t="s">
         <v>2251</v>
@@ -38886,34 +38888,34 @@
     </row>
     <row r="553" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B553">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C553" t="s">
         <v>950</v>
       </c>
       <c r="D553" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E553" t="s">
         <v>1307</v>
       </c>
-      <c r="E553" t="s">
-        <v>1308</v>
-      </c>
       <c r="F553" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="G553" t="s">
         <v>122</v>
       </c>
       <c r="H553" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I553" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="J553" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="K553" t="s">
         <v>105</v>
@@ -38940,7 +38942,7 @@
         <v>9354</v>
       </c>
       <c r="S553" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="T553" t="s">
         <v>2253</v>
@@ -38951,34 +38953,34 @@
     </row>
     <row r="554" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B554">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C554" t="s">
         <v>950</v>
       </c>
       <c r="D554" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E554" t="s">
         <v>1307</v>
       </c>
-      <c r="E554" t="s">
-        <v>1308</v>
-      </c>
       <c r="F554" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="G554" t="s">
         <v>122</v>
       </c>
       <c r="H554" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I554" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="J554" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="K554" t="s">
         <v>105</v>
@@ -39005,7 +39007,7 @@
         <v>9354</v>
       </c>
       <c r="S554" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="T554" t="s">
         <v>2255</v>
@@ -39016,34 +39018,34 @@
     </row>
     <row r="555" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B555">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C555" t="s">
         <v>950</v>
       </c>
       <c r="D555" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E555" t="s">
         <v>1307</v>
       </c>
-      <c r="E555" t="s">
-        <v>1308</v>
-      </c>
       <c r="F555" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="G555" t="s">
         <v>122</v>
       </c>
       <c r="H555" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I555" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="J555" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="K555" t="s">
         <v>105</v>
@@ -39070,7 +39072,7 @@
         <v>9354</v>
       </c>
       <c r="S555" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="T555" t="s">
         <v>2257</v>
@@ -39081,37 +39083,28 @@
     </row>
     <row r="556" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B556">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C556" t="s">
         <v>950</v>
       </c>
       <c r="D556" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E556" t="s">
         <v>1307</v>
       </c>
-      <c r="E556" t="s">
-        <v>1308</v>
-      </c>
       <c r="F556" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
       <c r="G556" t="s">
-        <v>122</v>
-      </c>
-      <c r="H556" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I556" t="s">
-        <v>1320</v>
-      </c>
-      <c r="J556" t="s">
-        <v>1327</v>
-      </c>
-      <c r="K556" t="s">
-        <v>105</v>
+        <v>1329</v>
       </c>
       <c r="L556" t="s">
         <v>712</v>
@@ -39119,11 +39112,11 @@
       <c r="M556" t="s">
         <v>712</v>
       </c>
-      <c r="N556">
-        <v>280</v>
+      <c r="N556" t="s">
+        <v>1330</v>
       </c>
       <c r="O556" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P556" t="s">
         <v>30</v>
@@ -39135,7 +39128,7 @@
         <v>9354</v>
       </c>
       <c r="S556" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="T556" t="s">
         <v>2259</v>
@@ -39146,28 +39139,37 @@
     </row>
     <row r="557" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B557">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C557" t="s">
         <v>950</v>
       </c>
       <c r="D557" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E557" t="s">
         <v>1307</v>
       </c>
-      <c r="E557" t="s">
-        <v>1308</v>
-      </c>
       <c r="F557" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="G557" t="s">
-        <v>40</v>
+        <v>130</v>
+      </c>
+      <c r="H557" t="s">
+        <v>34</v>
       </c>
       <c r="I557" t="s">
-        <v>1330</v>
+        <v>1333</v>
+      </c>
+      <c r="J557" t="s">
+        <v>1334</v>
+      </c>
+      <c r="K557" t="s">
+        <v>105</v>
       </c>
       <c r="L557" t="s">
         <v>712</v>
@@ -39175,11 +39177,11 @@
       <c r="M557" t="s">
         <v>712</v>
       </c>
-      <c r="N557" t="s">
-        <v>1331</v>
+      <c r="N557">
+        <v>285</v>
       </c>
       <c r="O557" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P557" t="s">
         <v>30</v>
@@ -39191,7 +39193,7 @@
         <v>9354</v>
       </c>
       <c r="S557" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="T557" t="s">
         <v>2261</v>
@@ -39202,34 +39204,34 @@
     </row>
     <row r="558" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B558">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C558" t="s">
         <v>950</v>
       </c>
       <c r="D558" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E558" t="s">
         <v>1307</v>
       </c>
-      <c r="E558" t="s">
-        <v>1308</v>
-      </c>
       <c r="F558" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="G558" t="s">
         <v>130</v>
       </c>
       <c r="H558" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I558" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="J558" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="K558" t="s">
         <v>105</v>
@@ -39256,7 +39258,7 @@
         <v>9354</v>
       </c>
       <c r="S558" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="T558" t="s">
         <v>2263</v>
@@ -39267,34 +39269,34 @@
     </row>
     <row r="559" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B559">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C559" t="s">
         <v>950</v>
       </c>
       <c r="D559" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E559" t="s">
         <v>1307</v>
       </c>
-      <c r="E559" t="s">
-        <v>1308</v>
-      </c>
       <c r="F559" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="G559" t="s">
         <v>130</v>
       </c>
       <c r="H559" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I559" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="J559" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="K559" t="s">
         <v>105</v>
@@ -39321,7 +39323,7 @@
         <v>9354</v>
       </c>
       <c r="S559" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="T559" t="s">
         <v>2265</v>
@@ -39332,34 +39334,34 @@
     </row>
     <row r="560" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B560">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C560" t="s">
         <v>950</v>
       </c>
       <c r="D560" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E560" t="s">
         <v>1307</v>
       </c>
-      <c r="E560" t="s">
-        <v>1308</v>
-      </c>
       <c r="F560" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="G560" t="s">
         <v>130</v>
       </c>
       <c r="H560" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I560" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="J560" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="K560" t="s">
         <v>105</v>
@@ -39386,7 +39388,7 @@
         <v>9354</v>
       </c>
       <c r="S560" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="T560" t="s">
         <v>2267</v>
@@ -39397,34 +39399,34 @@
     </row>
     <row r="561" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A561" s="1">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B561">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C561" t="s">
         <v>950</v>
       </c>
       <c r="D561" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E561" t="s">
         <v>1307</v>
       </c>
-      <c r="E561" t="s">
-        <v>1308</v>
-      </c>
       <c r="F561" t="s">
-        <v>1333</v>
+        <v>1342</v>
       </c>
       <c r="G561" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="H561" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I561" t="s">
-        <v>1334</v>
+        <v>1343</v>
       </c>
       <c r="J561" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="K561" t="s">
         <v>105</v>
@@ -39436,7 +39438,7 @@
         <v>712</v>
       </c>
       <c r="N561">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O561" t="s">
         <v>106</v>
@@ -39451,7 +39453,7 @@
         <v>9354</v>
       </c>
       <c r="S561" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="T561" t="s">
         <v>2269</v>
@@ -39462,34 +39464,34 @@
     </row>
     <row r="562" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A562" s="1">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B562">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C562" t="s">
         <v>950</v>
       </c>
       <c r="D562" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E562" t="s">
         <v>1307</v>
       </c>
-      <c r="E562" t="s">
-        <v>1308</v>
-      </c>
       <c r="F562" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G562" t="s">
         <v>143</v>
       </c>
       <c r="H562" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I562" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="J562" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="K562" t="s">
         <v>105</v>
@@ -39516,7 +39518,7 @@
         <v>9354</v>
       </c>
       <c r="S562" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="T562" t="s">
         <v>2271</v>
@@ -39527,34 +39529,34 @@
     </row>
     <row r="563" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A563" s="1">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B563">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C563" t="s">
         <v>950</v>
       </c>
       <c r="D563" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E563" t="s">
         <v>1307</v>
       </c>
-      <c r="E563" t="s">
-        <v>1308</v>
-      </c>
       <c r="F563" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G563" t="s">
         <v>143</v>
       </c>
       <c r="H563" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I563" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="J563" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="K563" t="s">
         <v>105</v>
@@ -39569,7 +39571,7 @@
         <v>287</v>
       </c>
       <c r="O563" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P563" t="s">
         <v>30</v>
@@ -39577,49 +39579,46 @@
       <c r="Q563" t="s">
         <v>30</v>
       </c>
-      <c r="R563">
-        <v>9354</v>
-      </c>
       <c r="S563" t="s">
-        <v>1348</v>
+        <v>30</v>
       </c>
       <c r="T563" t="s">
-        <v>2273</v>
+        <v>30</v>
       </c>
       <c r="U563" t="s">
-        <v>2274</v>
+        <v>30</v>
       </c>
     </row>
     <row r="564" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A564" s="1">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B564">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C564" t="s">
         <v>950</v>
       </c>
       <c r="D564" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E564" t="s">
         <v>1307</v>
       </c>
-      <c r="E564" t="s">
-        <v>1308</v>
-      </c>
       <c r="F564" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="G564" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H564" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I564" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="J564" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="K564" t="s">
         <v>105</v>
@@ -39631,10 +39630,10 @@
         <v>712</v>
       </c>
       <c r="N564">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O564" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P564" t="s">
         <v>30</v>
@@ -39642,46 +39641,49 @@
       <c r="Q564" t="s">
         <v>30</v>
       </c>
+      <c r="R564">
+        <v>9354</v>
+      </c>
       <c r="S564" t="s">
-        <v>30</v>
+        <v>1352</v>
       </c>
       <c r="T564" t="s">
-        <v>30</v>
+        <v>2273</v>
       </c>
       <c r="U564" t="s">
-        <v>30</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="565" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A565" s="1">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B565">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C565" t="s">
         <v>950</v>
       </c>
       <c r="D565" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E565" t="s">
         <v>1307</v>
       </c>
-      <c r="E565" t="s">
-        <v>1308</v>
-      </c>
       <c r="F565" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G565" t="s">
         <v>149</v>
       </c>
       <c r="H565" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I565" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J565" t="s">
-        <v>1352</v>
+        <v>1441</v>
       </c>
       <c r="K565" t="s">
         <v>105</v>
@@ -39719,31 +39721,31 @@
     </row>
     <row r="566" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A566" s="1">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B566">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C566" t="s">
         <v>950</v>
       </c>
       <c r="D566" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E566" t="s">
         <v>1307</v>
       </c>
-      <c r="E566" t="s">
-        <v>1308</v>
-      </c>
       <c r="F566" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G566" t="s">
         <v>149</v>
       </c>
       <c r="H566" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I566" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J566" t="s">
         <v>1354</v>
@@ -39784,31 +39786,31 @@
     </row>
     <row r="567" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A567" s="1">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B567">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C567" t="s">
         <v>950</v>
       </c>
       <c r="D567" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E567" t="s">
         <v>1307</v>
       </c>
-      <c r="E567" t="s">
-        <v>1308</v>
-      </c>
       <c r="F567" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G567" t="s">
         <v>149</v>
       </c>
       <c r="H567" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I567" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J567" t="s">
         <v>1356</v>
@@ -39849,34 +39851,34 @@
     </row>
     <row r="568" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A568" s="1">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B568">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C568" t="s">
         <v>950</v>
       </c>
       <c r="D568" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E568" t="s">
         <v>1307</v>
       </c>
-      <c r="E568" t="s">
-        <v>1308</v>
-      </c>
       <c r="F568" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="G568" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H568" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I568" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="J568" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="K568" t="s">
         <v>105</v>
@@ -39888,7 +39890,7 @@
         <v>712</v>
       </c>
       <c r="N568">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O568" t="s">
         <v>106</v>
@@ -39903,7 +39905,7 @@
         <v>9354</v>
       </c>
       <c r="S568" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="T568" t="s">
         <v>2281</v>
@@ -39914,31 +39916,31 @@
     </row>
     <row r="569" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A569" s="1">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B569">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C569" t="s">
         <v>950</v>
       </c>
       <c r="D569" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E569" t="s">
         <v>1307</v>
       </c>
-      <c r="E569" t="s">
-        <v>1308</v>
-      </c>
       <c r="F569" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="G569" t="s">
         <v>152</v>
       </c>
       <c r="H569" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I569" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J569" t="s">
         <v>1362</v>
@@ -39979,31 +39981,31 @@
     </row>
     <row r="570" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A570" s="1">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B570">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C570" t="s">
         <v>950</v>
       </c>
       <c r="D570" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E570" t="s">
         <v>1307</v>
       </c>
-      <c r="E570" t="s">
-        <v>1308</v>
-      </c>
       <c r="F570" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="G570" t="s">
         <v>152</v>
       </c>
       <c r="H570" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I570" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J570" t="s">
         <v>1364</v>
@@ -40044,31 +40046,31 @@
     </row>
     <row r="571" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A571" s="1">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B571">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C571" t="s">
         <v>950</v>
       </c>
       <c r="D571" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E571" t="s">
         <v>1307</v>
       </c>
-      <c r="E571" t="s">
-        <v>1308</v>
-      </c>
       <c r="F571" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="G571" t="s">
         <v>152</v>
       </c>
       <c r="H571" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I571" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J571" t="s">
         <v>1366</v>
@@ -40109,37 +40111,31 @@
     </row>
     <row r="572" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A572" s="1">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B572">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C572" t="s">
         <v>950</v>
       </c>
       <c r="D572" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E572" t="s">
         <v>1307</v>
       </c>
-      <c r="E572" t="s">
-        <v>1308</v>
-      </c>
       <c r="F572" t="s">
-        <v>1360</v>
+        <v>1369</v>
       </c>
       <c r="G572" t="s">
-        <v>152</v>
-      </c>
-      <c r="H572" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="I572" t="s">
-        <v>1361</v>
-      </c>
-      <c r="J572" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="K572" t="s">
-        <v>105</v>
+        <v>1000</v>
       </c>
       <c r="L572" t="s">
         <v>712</v>
@@ -40148,7 +40144,7 @@
         <v>712</v>
       </c>
       <c r="N572">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O572" t="s">
         <v>106</v>
@@ -40163,7 +40159,7 @@
         <v>9354</v>
       </c>
       <c r="S572" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="T572" t="s">
         <v>2289</v>
@@ -40174,25 +40170,25 @@
     </row>
     <row r="573" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A573" s="1">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B573">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C573" t="s">
         <v>950</v>
       </c>
       <c r="D573" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E573" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F573" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="G573" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I573" t="s">
         <v>1372</v>
@@ -40233,25 +40229,25 @@
     </row>
     <row r="574" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A574" s="1">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B574">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C574" t="s">
         <v>950</v>
       </c>
       <c r="D574" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E574" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F574" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="G574" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I574" t="s">
         <v>1374</v>
@@ -40292,31 +40288,31 @@
     </row>
     <row r="575" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A575" s="1">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B575">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C575" t="s">
         <v>950</v>
       </c>
       <c r="D575" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E575" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F575" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="G575" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="I575" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="K575" t="s">
-        <v>1000</v>
+        <v>188</v>
       </c>
       <c r="L575" t="s">
         <v>712</v>
@@ -40325,7 +40321,7 @@
         <v>712</v>
       </c>
       <c r="N575">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O575" t="s">
         <v>106</v>
@@ -40340,7 +40336,7 @@
         <v>9354</v>
       </c>
       <c r="S575" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="T575" t="s">
         <v>2295</v>
@@ -40351,25 +40347,25 @@
     </row>
     <row r="576" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A576" s="1">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B576">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C576" t="s">
         <v>950</v>
       </c>
       <c r="D576" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E576" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F576" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G576" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="I576" t="s">
         <v>1379</v>
@@ -40410,25 +40406,25 @@
     </row>
     <row r="577" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A577" s="1">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B577">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C577" t="s">
         <v>950</v>
       </c>
       <c r="D577" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E577" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F577" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G577" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="I577" t="s">
         <v>1381</v>
@@ -40469,25 +40465,25 @@
     </row>
     <row r="578" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A578" s="1">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B578">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C578" t="s">
         <v>950</v>
       </c>
       <c r="D578" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E578" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F578" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G578" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I578" t="s">
         <v>1383</v>
@@ -40528,25 +40524,25 @@
     </row>
     <row r="579" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A579" s="1">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B579">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C579" t="s">
         <v>950</v>
       </c>
       <c r="D579" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E579" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F579" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G579" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I579" t="s">
         <v>1385</v>
@@ -40587,25 +40583,25 @@
     </row>
     <row r="580" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A580" s="1">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B580">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C580" t="s">
         <v>950</v>
       </c>
       <c r="D580" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E580" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F580" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G580" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I580" t="s">
         <v>1387</v>
@@ -40646,25 +40642,25 @@
     </row>
     <row r="581" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A581" s="1">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B581">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C581" t="s">
         <v>950</v>
       </c>
       <c r="D581" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E581" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F581" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G581" t="s">
-        <v>152</v>
+        <v>796</v>
       </c>
       <c r="I581" t="s">
         <v>1389</v>
@@ -40705,25 +40701,25 @@
     </row>
     <row r="582" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A582" s="1">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B582">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C582" t="s">
         <v>950</v>
       </c>
       <c r="D582" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E582" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F582" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G582" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="I582" t="s">
         <v>1391</v>
@@ -40764,28 +40760,28 @@
     </row>
     <row r="583" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A583" s="1">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B583">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C583" t="s">
         <v>950</v>
       </c>
       <c r="D583" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E583" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F583" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="G583" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="I583" t="s">
-        <v>1393</v>
+        <v>715</v>
       </c>
       <c r="K583" t="s">
         <v>188</v>
@@ -40812,7 +40808,7 @@
         <v>9354</v>
       </c>
       <c r="S583" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="T583" t="s">
         <v>2311</v>
@@ -40823,43 +40819,37 @@
     </row>
     <row r="584" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A584" s="1">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B584">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C584" t="s">
         <v>950</v>
       </c>
       <c r="D584" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E584" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F584" t="s">
-        <v>1378</v>
+        <v>1394</v>
       </c>
       <c r="G584" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="I584" t="s">
-        <v>715</v>
+        <v>1395</v>
       </c>
       <c r="K584" t="s">
         <v>188</v>
       </c>
-      <c r="L584" t="s">
-        <v>712</v>
-      </c>
-      <c r="M584" t="s">
-        <v>712</v>
-      </c>
       <c r="N584">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O584" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P584" t="s">
         <v>30</v>
@@ -40867,49 +40857,46 @@
       <c r="Q584" t="s">
         <v>30</v>
       </c>
-      <c r="R584">
-        <v>9354</v>
-      </c>
       <c r="S584" t="s">
-        <v>1395</v>
+        <v>30</v>
       </c>
       <c r="T584" t="s">
-        <v>2313</v>
+        <v>30</v>
       </c>
       <c r="U584" t="s">
-        <v>2314</v>
+        <v>30</v>
       </c>
     </row>
     <row r="585" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A585" s="1">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B585">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C585" t="s">
         <v>950</v>
       </c>
       <c r="D585" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E585" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F585" t="s">
         <v>1396</v>
       </c>
       <c r="G585" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="I585" t="s">
         <v>1397</v>
       </c>
       <c r="K585" t="s">
-        <v>188</v>
-      </c>
-      <c r="N585">
-        <v>293</v>
+        <v>1245</v>
+      </c>
+      <c r="N585" t="s">
+        <v>1398</v>
       </c>
       <c r="O585" t="s">
         <v>30</v>
@@ -40920,49 +40907,55 @@
       <c r="Q585" t="s">
         <v>30</v>
       </c>
+      <c r="R585">
+        <v>9354</v>
+      </c>
       <c r="S585" t="s">
-        <v>30</v>
+        <v>1399</v>
       </c>
       <c r="T585" t="s">
-        <v>30</v>
+        <v>2313</v>
       </c>
       <c r="U585" t="s">
-        <v>30</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="586" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A586" s="1">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B586">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C586" t="s">
         <v>950</v>
       </c>
       <c r="D586" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E586" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F586" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="G586" t="s">
         <v>810</v>
       </c>
+      <c r="H586" t="s">
+        <v>34</v>
+      </c>
       <c r="I586" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="K586" t="s">
-        <v>1245</v>
+        <v>967</v>
       </c>
       <c r="N586" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="O586" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P586" t="s">
         <v>30</v>
@@ -40985,40 +40978,37 @@
     </row>
     <row r="587" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A587" s="1">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B587">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C587" t="s">
         <v>950</v>
       </c>
       <c r="D587" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E587" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F587" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="G587" t="s">
         <v>810</v>
       </c>
-      <c r="H587" t="s">
-        <v>34</v>
-      </c>
       <c r="I587" t="s">
         <v>1402</v>
       </c>
       <c r="K587" t="s">
-        <v>967</v>
+        <v>1403</v>
       </c>
       <c r="N587" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="O587" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P587" t="s">
         <v>30</v>
@@ -41026,37 +41016,34 @@
       <c r="Q587" t="s">
         <v>30</v>
       </c>
-      <c r="R587">
-        <v>9354</v>
-      </c>
       <c r="S587" t="s">
-        <v>1403</v>
+        <v>30</v>
       </c>
       <c r="T587" t="s">
-        <v>2317</v>
+        <v>30</v>
       </c>
       <c r="U587" t="s">
-        <v>2318</v>
+        <v>30</v>
       </c>
     </row>
     <row r="588" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A588" s="1">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B588">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C588" t="s">
         <v>950</v>
       </c>
       <c r="D588" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E588" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F588" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="G588" t="s">
         <v>810</v>
@@ -41065,10 +41052,10 @@
         <v>1404</v>
       </c>
       <c r="K588" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="N588" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="O588" t="s">
         <v>30</v>
@@ -41091,37 +41078,43 @@
     </row>
     <row r="589" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A589" s="1">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B589">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C589" t="s">
         <v>950</v>
       </c>
       <c r="D589" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E589" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F589" t="s">
-        <v>1398</v>
+        <v>1405</v>
       </c>
       <c r="G589" t="s">
-        <v>810</v>
+        <v>814</v>
+      </c>
+      <c r="H589" t="s">
+        <v>34</v>
       </c>
       <c r="I589" t="s">
         <v>1406</v>
       </c>
+      <c r="J589" t="s">
+        <v>1407</v>
+      </c>
       <c r="K589" t="s">
-        <v>1405</v>
-      </c>
-      <c r="N589" t="s">
-        <v>1400</v>
+        <v>1148</v>
+      </c>
+      <c r="N589">
+        <v>297</v>
       </c>
       <c r="O589" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P589" t="s">
         <v>30</v>
@@ -41129,43 +41122,46 @@
       <c r="Q589" t="s">
         <v>30</v>
       </c>
+      <c r="R589">
+        <v>9354</v>
+      </c>
       <c r="S589" t="s">
-        <v>30</v>
+        <v>1408</v>
       </c>
       <c r="T589" t="s">
-        <v>30</v>
+        <v>2317</v>
       </c>
       <c r="U589" t="s">
-        <v>30</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="590" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A590" s="1">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B590">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C590" t="s">
         <v>950</v>
       </c>
       <c r="D590" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E590" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F590" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="G590" t="s">
         <v>814</v>
       </c>
       <c r="H590" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I590" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="J590" t="s">
         <v>1409</v>
@@ -41200,43 +41196,43 @@
     </row>
     <row r="591" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A591" s="1">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B591">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C591" t="s">
         <v>950</v>
       </c>
       <c r="D591" t="s">
-        <v>1370</v>
+        <v>1411</v>
       </c>
       <c r="E591" t="s">
-        <v>1308</v>
+        <v>1412</v>
       </c>
       <c r="F591" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="G591" t="s">
-        <v>814</v>
-      </c>
-      <c r="H591" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I591" t="s">
-        <v>1408</v>
-      </c>
-      <c r="J591" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="K591" t="s">
-        <v>1148</v>
-      </c>
-      <c r="N591">
-        <v>297</v>
+        <v>196</v>
+      </c>
+      <c r="L591" t="s">
+        <v>712</v>
+      </c>
+      <c r="M591" t="s">
+        <v>712</v>
+      </c>
+      <c r="N591" t="s">
+        <v>1415</v>
       </c>
       <c r="O591" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P591" t="s">
         <v>30</v>
@@ -41248,7 +41244,7 @@
         <v>9354</v>
       </c>
       <c r="S591" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="T591" t="s">
         <v>2321</v>
@@ -41259,31 +41255,31 @@
     </row>
     <row r="592" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A592" s="1">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B592">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C592" t="s">
         <v>950</v>
       </c>
       <c r="D592" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E592" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F592" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="G592" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I592" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="K592" t="s">
-        <v>196</v>
+        <v>620</v>
       </c>
       <c r="L592" t="s">
         <v>712</v>
@@ -41291,8 +41287,8 @@
       <c r="M592" t="s">
         <v>712</v>
       </c>
-      <c r="N592" t="s">
-        <v>1417</v>
+      <c r="N592">
+        <v>302</v>
       </c>
       <c r="O592" t="s">
         <v>30</v>
@@ -41303,46 +41299,43 @@
       <c r="Q592" t="s">
         <v>30</v>
       </c>
-      <c r="R592">
-        <v>9354</v>
-      </c>
       <c r="S592" t="s">
-        <v>1418</v>
+        <v>30</v>
       </c>
       <c r="T592" t="s">
-        <v>2323</v>
+        <v>30</v>
       </c>
       <c r="U592" t="s">
-        <v>2324</v>
+        <v>30</v>
       </c>
     </row>
     <row r="593" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A593" s="1">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B593">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C593" t="s">
         <v>950</v>
       </c>
       <c r="D593" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E593" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F593" t="s">
         <v>1419</v>
       </c>
       <c r="G593" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I593" t="s">
-        <v>1420</v>
+        <v>1372</v>
       </c>
       <c r="K593" t="s">
-        <v>620</v>
+        <v>196</v>
       </c>
       <c r="L593" t="s">
         <v>712</v>
@@ -41350,8 +41343,8 @@
       <c r="M593" t="s">
         <v>712</v>
       </c>
-      <c r="N593">
-        <v>302</v>
+      <c r="N593" t="s">
+        <v>1420</v>
       </c>
       <c r="O593" t="s">
         <v>30</v>
@@ -41362,43 +41355,46 @@
       <c r="Q593" t="s">
         <v>30</v>
       </c>
+      <c r="R593">
+        <v>9354</v>
+      </c>
       <c r="S593" t="s">
-        <v>30</v>
+        <v>1421</v>
       </c>
       <c r="T593" t="s">
-        <v>30</v>
+        <v>2323</v>
       </c>
       <c r="U593" t="s">
-        <v>30</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="594" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A594" s="1">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B594">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C594" t="s">
         <v>950</v>
       </c>
       <c r="D594" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E594" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F594" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="G594" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="I594" t="s">
-        <v>1374</v>
+        <v>1423</v>
       </c>
       <c r="K594" t="s">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="L594" t="s">
         <v>712</v>
@@ -41406,11 +41402,11 @@
       <c r="M594" t="s">
         <v>712</v>
       </c>
-      <c r="N594" t="s">
-        <v>1422</v>
+      <c r="N594">
+        <v>307</v>
       </c>
       <c r="O594" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P594" t="s">
         <v>30</v>
@@ -41422,7 +41418,7 @@
         <v>9354</v>
       </c>
       <c r="S594" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="T594" t="s">
         <v>2325</v>
@@ -41433,31 +41429,31 @@
     </row>
     <row r="595" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A595" s="1">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B595">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C595" t="s">
         <v>950</v>
       </c>
       <c r="D595" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E595" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F595" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="G595" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="I595" t="s">
-        <v>1425</v>
+        <v>1374</v>
       </c>
       <c r="K595" t="s">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="L595" t="s">
         <v>712</v>
@@ -41465,11 +41461,11 @@
       <c r="M595" t="s">
         <v>712</v>
       </c>
-      <c r="N595">
-        <v>307</v>
+      <c r="N595" t="s">
+        <v>1426</v>
       </c>
       <c r="O595" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P595" t="s">
         <v>30</v>
@@ -41481,7 +41477,7 @@
         <v>9354</v>
       </c>
       <c r="S595" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="T595" t="s">
         <v>2327</v>
@@ -41492,31 +41488,37 @@
     </row>
     <row r="596" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A596" s="1">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B596">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C596" t="s">
         <v>950</v>
       </c>
       <c r="D596" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E596" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F596" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G596" t="s">
-        <v>40</v>
+        <v>130</v>
+      </c>
+      <c r="H596" t="s">
+        <v>34</v>
       </c>
       <c r="I596" t="s">
-        <v>1376</v>
+        <v>1429</v>
+      </c>
+      <c r="J596" t="s">
+        <v>1334</v>
       </c>
       <c r="K596" t="s">
-        <v>196</v>
+        <v>105</v>
       </c>
       <c r="L596" t="s">
         <v>712</v>
@@ -41524,11 +41526,11 @@
       <c r="M596" t="s">
         <v>712</v>
       </c>
-      <c r="N596" t="s">
-        <v>1428</v>
+      <c r="N596">
+        <v>312</v>
       </c>
       <c r="O596" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P596" t="s">
         <v>30</v>
@@ -41540,7 +41542,7 @@
         <v>9354</v>
       </c>
       <c r="S596" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="T596" t="s">
         <v>2329</v>
@@ -41551,34 +41553,34 @@
     </row>
     <row r="597" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A597" s="1">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B597">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C597" t="s">
         <v>950</v>
       </c>
       <c r="D597" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E597" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F597" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G597" t="s">
         <v>130</v>
       </c>
       <c r="H597" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I597" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="J597" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="K597" t="s">
         <v>105</v>
@@ -41605,7 +41607,7 @@
         <v>9354</v>
       </c>
       <c r="S597" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="T597" t="s">
         <v>2331</v>
@@ -41616,34 +41618,34 @@
     </row>
     <row r="598" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A598" s="1">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B598">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C598" t="s">
         <v>950</v>
       </c>
       <c r="D598" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E598" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F598" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G598" t="s">
         <v>130</v>
       </c>
       <c r="H598" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I598" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="J598" t="s">
-        <v>1337</v>
+        <v>1432</v>
       </c>
       <c r="K598" t="s">
         <v>105</v>
@@ -41681,31 +41683,31 @@
     </row>
     <row r="599" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A599" s="1">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B599">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C599" t="s">
         <v>950</v>
       </c>
       <c r="D599" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E599" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F599" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G599" t="s">
         <v>130</v>
       </c>
       <c r="H599" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I599" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="J599" t="s">
         <v>1434</v>
@@ -41746,34 +41748,34 @@
     </row>
     <row r="600" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A600" s="1">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B600">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C600" t="s">
         <v>950</v>
       </c>
       <c r="D600" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E600" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F600" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="G600" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="H600" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I600" t="s">
-        <v>1431</v>
+        <v>1343</v>
       </c>
       <c r="J600" t="s">
-        <v>1436</v>
+        <v>1344</v>
       </c>
       <c r="K600" t="s">
         <v>105</v>
@@ -41785,7 +41787,7 @@
         <v>712</v>
       </c>
       <c r="N600">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O600" t="s">
         <v>106</v>
@@ -41811,34 +41813,34 @@
     </row>
     <row r="601" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A601" s="1">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B601">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C601" t="s">
         <v>950</v>
       </c>
       <c r="D601" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E601" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F601" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="G601" t="s">
         <v>143</v>
       </c>
       <c r="H601" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I601" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="J601" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="K601" t="s">
         <v>105</v>
@@ -41865,7 +41867,7 @@
         <v>9354</v>
       </c>
       <c r="S601" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="T601" t="s">
         <v>2339</v>
@@ -41876,37 +41878,37 @@
     </row>
     <row r="602" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A602" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B602">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C602" t="s">
         <v>950</v>
       </c>
       <c r="D602" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E602" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F602" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="G602" t="s">
         <v>143</v>
       </c>
       <c r="H602" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I602" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="J602" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="K602" t="s">
-        <v>105</v>
+        <v>620</v>
       </c>
       <c r="L602" t="s">
         <v>712</v>
@@ -41918,7 +41920,7 @@
         <v>314</v>
       </c>
       <c r="O602" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P602" t="s">
         <v>30</v>
@@ -41926,52 +41928,49 @@
       <c r="Q602" t="s">
         <v>30</v>
       </c>
-      <c r="R602">
-        <v>9354</v>
-      </c>
       <c r="S602" t="s">
-        <v>1440</v>
+        <v>30</v>
       </c>
       <c r="T602" t="s">
-        <v>2341</v>
+        <v>30</v>
       </c>
       <c r="U602" t="s">
-        <v>2342</v>
+        <v>30</v>
       </c>
     </row>
     <row r="603" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A603" s="1">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B603">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C603" t="s">
         <v>950</v>
       </c>
       <c r="D603" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E603" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F603" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="G603" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H603" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I603" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="J603" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="K603" t="s">
-        <v>620</v>
+        <v>105</v>
       </c>
       <c r="L603" t="s">
         <v>712</v>
@@ -41980,10 +41979,10 @@
         <v>712</v>
       </c>
       <c r="N603">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O603" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P603" t="s">
         <v>30</v>
@@ -41991,46 +41990,49 @@
       <c r="Q603" t="s">
         <v>30</v>
       </c>
+      <c r="R603">
+        <v>9354</v>
+      </c>
       <c r="S603" t="s">
-        <v>30</v>
+        <v>1440</v>
       </c>
       <c r="T603" t="s">
-        <v>30</v>
+        <v>2341</v>
       </c>
       <c r="U603" t="s">
-        <v>30</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="604" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A604" s="1">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B604">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C604" t="s">
         <v>950</v>
       </c>
       <c r="D604" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E604" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F604" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G604" t="s">
         <v>149</v>
       </c>
       <c r="H604" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I604" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J604" t="s">
-        <v>1352</v>
+        <v>1441</v>
       </c>
       <c r="K604" t="s">
         <v>105</v>
@@ -42068,34 +42070,34 @@
     </row>
     <row r="605" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A605" s="1">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B605">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C605" t="s">
         <v>950</v>
       </c>
       <c r="D605" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E605" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F605" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G605" t="s">
         <v>149</v>
       </c>
       <c r="H605" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I605" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J605" t="s">
-        <v>1443</v>
+        <v>1354</v>
       </c>
       <c r="K605" t="s">
         <v>105</v>
@@ -42122,7 +42124,7 @@
         <v>9354</v>
       </c>
       <c r="S605" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="T605" t="s">
         <v>2345</v>
@@ -42133,31 +42135,31 @@
     </row>
     <row r="606" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A606" s="1">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B606">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C606" t="s">
         <v>950</v>
       </c>
       <c r="D606" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E606" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F606" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G606" t="s">
         <v>149</v>
       </c>
       <c r="H606" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I606" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J606" t="s">
         <v>1356</v>
@@ -42187,7 +42189,7 @@
         <v>9354</v>
       </c>
       <c r="S606" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="T606" t="s">
         <v>2347</v>
@@ -42198,34 +42200,34 @@
     </row>
     <row r="607" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A607" s="1">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B607">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C607" t="s">
         <v>950</v>
       </c>
       <c r="D607" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E607" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F607" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="G607" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H607" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I607" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="J607" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="K607" t="s">
         <v>105</v>
@@ -42237,7 +42239,7 @@
         <v>712</v>
       </c>
       <c r="N607">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O607" t="s">
         <v>106</v>
@@ -42263,31 +42265,31 @@
     </row>
     <row r="608" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A608" s="1">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B608">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C608" t="s">
         <v>950</v>
       </c>
       <c r="D608" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E608" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F608" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G608" t="s">
         <v>152</v>
       </c>
       <c r="H608" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I608" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J608" t="s">
         <v>1362</v>
@@ -42317,7 +42319,7 @@
         <v>9354</v>
       </c>
       <c r="S608" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="T608" t="s">
         <v>2351</v>
@@ -42328,31 +42330,31 @@
     </row>
     <row r="609" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A609" s="1">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B609">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C609" t="s">
         <v>950</v>
       </c>
       <c r="D609" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E609" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F609" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G609" t="s">
         <v>152</v>
       </c>
       <c r="H609" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I609" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J609" t="s">
         <v>1364</v>
@@ -42382,7 +42384,7 @@
         <v>9354</v>
       </c>
       <c r="S609" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="T609" t="s">
         <v>2353</v>
@@ -42393,31 +42395,31 @@
     </row>
     <row r="610" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A610" s="1">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B610">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C610" t="s">
         <v>950</v>
       </c>
       <c r="D610" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E610" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F610" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G610" t="s">
         <v>152</v>
       </c>
       <c r="H610" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I610" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="J610" t="s">
         <v>1366</v>
@@ -42447,7 +42449,7 @@
         <v>9354</v>
       </c>
       <c r="S610" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="T610" t="s">
         <v>2355</v>
@@ -42458,46 +42460,34 @@
     </row>
     <row r="611" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A611" s="1">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B611">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C611" t="s">
         <v>950</v>
       </c>
       <c r="D611" t="s">
-        <v>1413</v>
+        <v>1450</v>
       </c>
       <c r="E611" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F611" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="G611" t="s">
-        <v>152</v>
-      </c>
-      <c r="H611" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="I611" t="s">
-        <v>1361</v>
-      </c>
-      <c r="J611" t="s">
-        <v>1368</v>
+        <v>1452</v>
       </c>
       <c r="K611" t="s">
-        <v>105</v>
-      </c>
-      <c r="L611" t="s">
-        <v>712</v>
-      </c>
-      <c r="M611" t="s">
-        <v>712</v>
+        <v>188</v>
       </c>
       <c r="N611">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O611" t="s">
         <v>106</v>
@@ -42512,7 +42502,7 @@
         <v>9354</v>
       </c>
       <c r="S611" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="T611" t="s">
         <v>2357</v>
@@ -42523,31 +42513,31 @@
     </row>
     <row r="612" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A612" s="1">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B612">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C612" t="s">
         <v>950</v>
       </c>
       <c r="D612" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E612" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F612" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="G612" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I612" t="s">
-        <v>1454</v>
+        <v>1372</v>
       </c>
       <c r="K612" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N612">
         <v>318</v>
@@ -42565,7 +42555,7 @@
         <v>9354</v>
       </c>
       <c r="S612" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="T612" t="s">
         <v>2359</v>
@@ -42576,25 +42566,25 @@
     </row>
     <row r="613" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A613" s="1">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B613">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C613" t="s">
         <v>950</v>
       </c>
       <c r="D613" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E613" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F613" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="G613" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I613" t="s">
         <v>1374</v>
@@ -42618,7 +42608,7 @@
         <v>9354</v>
       </c>
       <c r="S613" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="T613" t="s">
         <v>2361</v>
@@ -42629,28 +42619,28 @@
     </row>
     <row r="614" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A614" s="1">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B614">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C614" t="s">
         <v>950</v>
       </c>
       <c r="D614" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E614" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F614" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="G614" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="I614" t="s">
-        <v>1376</v>
+        <v>1456</v>
       </c>
       <c r="K614" t="s">
         <v>196</v>
@@ -42682,34 +42672,34 @@
     </row>
     <row r="615" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A615" s="1">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B615">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C615" t="s">
         <v>950</v>
       </c>
       <c r="D615" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E615" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F615" t="s">
-        <v>1453</v>
+        <v>1458</v>
       </c>
       <c r="G615" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="I615" t="s">
-        <v>1458</v>
+        <v>1379</v>
       </c>
       <c r="K615" t="s">
         <v>196</v>
       </c>
       <c r="N615">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O615" t="s">
         <v>106</v>
@@ -42735,25 +42725,25 @@
     </row>
     <row r="616" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A616" s="1">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B616">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C616" t="s">
         <v>950</v>
       </c>
       <c r="D616" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E616" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F616" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G616" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="I616" t="s">
         <v>1381</v>
@@ -42777,7 +42767,7 @@
         <v>9354</v>
       </c>
       <c r="S616" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="T616" t="s">
         <v>2367</v>
@@ -42788,25 +42778,25 @@
     </row>
     <row r="617" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A617" s="1">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B617">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C617" t="s">
         <v>950</v>
       </c>
       <c r="D617" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E617" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F617" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G617" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I617" t="s">
         <v>1383</v>
@@ -42830,7 +42820,7 @@
         <v>9354</v>
       </c>
       <c r="S617" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="T617" t="s">
         <v>2369</v>
@@ -42841,25 +42831,25 @@
     </row>
     <row r="618" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A618" s="1">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B618">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C618" t="s">
         <v>950</v>
       </c>
       <c r="D618" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E618" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F618" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G618" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I618" t="s">
         <v>1385</v>
@@ -42883,7 +42873,7 @@
         <v>9354</v>
       </c>
       <c r="S618" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="T618" t="s">
         <v>2371</v>
@@ -42894,25 +42884,25 @@
     </row>
     <row r="619" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A619" s="1">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B619">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C619" t="s">
         <v>950</v>
       </c>
       <c r="D619" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E619" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F619" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G619" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I619" t="s">
         <v>1387</v>
@@ -42936,7 +42926,7 @@
         <v>9354</v>
       </c>
       <c r="S619" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="T619" t="s">
         <v>2373</v>
@@ -42947,25 +42937,25 @@
     </row>
     <row r="620" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A620" s="1">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B620">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C620" t="s">
         <v>950</v>
       </c>
       <c r="D620" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E620" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F620" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G620" t="s">
-        <v>152</v>
+        <v>796</v>
       </c>
       <c r="I620" t="s">
         <v>1389</v>
@@ -42989,7 +42979,7 @@
         <v>9354</v>
       </c>
       <c r="S620" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="T620" t="s">
         <v>2375</v>
@@ -43000,25 +42990,25 @@
     </row>
     <row r="621" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A621" s="1">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B621">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C621" t="s">
         <v>950</v>
       </c>
       <c r="D621" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E621" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F621" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G621" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="I621" t="s">
         <v>1391</v>
@@ -43042,7 +43032,7 @@
         <v>9354</v>
       </c>
       <c r="S621" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="T621" t="s">
         <v>2377</v>
@@ -43053,28 +43043,28 @@
     </row>
     <row r="622" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A622" s="1">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B622">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C622" t="s">
         <v>950</v>
       </c>
       <c r="D622" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E622" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F622" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G622" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="I622" t="s">
-        <v>1393</v>
+        <v>715</v>
       </c>
       <c r="K622" t="s">
         <v>196</v>
@@ -43095,7 +43085,7 @@
         <v>9354</v>
       </c>
       <c r="S622" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="T622" t="s">
         <v>2379</v>
@@ -43106,37 +43096,37 @@
     </row>
     <row r="623" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A623" s="1">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B623">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C623" t="s">
         <v>950</v>
       </c>
       <c r="D623" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="E623" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F623" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="G623" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="I623" t="s">
-        <v>715</v>
+        <v>1468</v>
       </c>
       <c r="K623" t="s">
         <v>196</v>
       </c>
       <c r="N623">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O623" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P623" t="s">
         <v>30</v>
@@ -43144,52 +43134,49 @@
       <c r="Q623" t="s">
         <v>30</v>
       </c>
-      <c r="R623">
-        <v>9354</v>
-      </c>
       <c r="S623" t="s">
-        <v>1468</v>
+        <v>30</v>
       </c>
       <c r="T623" t="s">
-        <v>2381</v>
+        <v>30</v>
       </c>
       <c r="U623" t="s">
-        <v>2382</v>
+        <v>30</v>
       </c>
     </row>
     <row r="624" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A624" s="1">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B624">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C624" t="s">
         <v>950</v>
       </c>
       <c r="D624" t="s">
-        <v>1452</v>
+        <v>1469</v>
       </c>
       <c r="E624" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F624" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="G624" t="s">
-        <v>807</v>
+        <v>31</v>
       </c>
       <c r="I624" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="K624" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N624">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O624" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="P624" t="s">
         <v>30</v>
@@ -43197,40 +43184,43 @@
       <c r="Q624" t="s">
         <v>30</v>
       </c>
+      <c r="R624">
+        <v>9354</v>
+      </c>
       <c r="S624" t="s">
-        <v>30</v>
+        <v>1472</v>
       </c>
       <c r="T624" t="s">
-        <v>30</v>
+        <v>2381</v>
       </c>
       <c r="U624" t="s">
-        <v>30</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="625" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A625" s="1">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B625">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C625" t="s">
         <v>950</v>
       </c>
       <c r="D625" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E625" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F625" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="G625" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I625" t="s">
-        <v>1473</v>
+        <v>1456</v>
       </c>
       <c r="K625" t="s">
         <v>188</v>
@@ -43251,7 +43241,7 @@
         <v>9354</v>
       </c>
       <c r="S625" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="T625" t="s">
         <v>2383</v>
@@ -43262,34 +43252,34 @@
     </row>
     <row r="626" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A626" s="1">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B626">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C626" t="s">
         <v>950</v>
       </c>
       <c r="D626" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E626" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F626" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="G626" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I626" t="s">
-        <v>1458</v>
+        <v>1379</v>
       </c>
       <c r="K626" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N626">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O626" t="s">
         <v>106</v>
@@ -43315,25 +43305,25 @@
     </row>
     <row r="627" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A627" s="1">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B627">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C627" t="s">
         <v>950</v>
       </c>
       <c r="D627" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E627" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F627" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G627" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="I627" t="s">
         <v>1381</v>
@@ -43357,7 +43347,7 @@
         <v>9354</v>
       </c>
       <c r="S627" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="T627" t="s">
         <v>2387</v>
@@ -43368,25 +43358,25 @@
     </row>
     <row r="628" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A628" s="1">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B628">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C628" t="s">
         <v>950</v>
       </c>
       <c r="D628" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E628" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F628" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G628" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="I628" t="s">
         <v>1383</v>
@@ -43410,7 +43400,7 @@
         <v>9354</v>
       </c>
       <c r="S628" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="T628" t="s">
         <v>2389</v>
@@ -43421,25 +43411,25 @@
     </row>
     <row r="629" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A629" s="1">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B629">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C629" t="s">
         <v>950</v>
       </c>
       <c r="D629" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E629" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F629" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G629" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="I629" t="s">
         <v>1385</v>
@@ -43463,7 +43453,7 @@
         <v>9354</v>
       </c>
       <c r="S629" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="T629" t="s">
         <v>2391</v>
@@ -43474,25 +43464,25 @@
     </row>
     <row r="630" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A630" s="1">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B630">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C630" t="s">
         <v>950</v>
       </c>
       <c r="D630" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E630" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F630" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G630" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I630" t="s">
         <v>1387</v>
@@ -43516,7 +43506,7 @@
         <v>9354</v>
       </c>
       <c r="S630" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="T630" t="s">
         <v>2393</v>
@@ -43527,25 +43517,25 @@
     </row>
     <row r="631" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A631" s="1">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B631">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C631" t="s">
         <v>950</v>
       </c>
       <c r="D631" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E631" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F631" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G631" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="I631" t="s">
         <v>1389</v>
@@ -43569,7 +43559,7 @@
         <v>9354</v>
       </c>
       <c r="S631" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="T631" t="s">
         <v>2395</v>
@@ -43580,25 +43570,25 @@
     </row>
     <row r="632" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A632" s="1">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B632">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C632" t="s">
         <v>950</v>
       </c>
       <c r="D632" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E632" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F632" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G632" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I632" t="s">
         <v>1391</v>
@@ -43622,7 +43612,7 @@
         <v>9354</v>
       </c>
       <c r="S632" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="T632" t="s">
         <v>2397</v>
@@ -43633,28 +43623,28 @@
     </row>
     <row r="633" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A633" s="1">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B633">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C633" t="s">
         <v>950</v>
       </c>
       <c r="D633" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E633" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F633" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="G633" t="s">
-        <v>152</v>
+        <v>796</v>
       </c>
       <c r="I633" t="s">
-        <v>1393</v>
+        <v>715</v>
       </c>
       <c r="K633" t="s">
         <v>196</v>
@@ -43675,7 +43665,7 @@
         <v>9354</v>
       </c>
       <c r="S633" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="T633" t="s">
         <v>2399</v>
@@ -43686,37 +43676,37 @@
     </row>
     <row r="634" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A634" s="1">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B634">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C634" t="s">
         <v>950</v>
       </c>
       <c r="D634" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="E634" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F634" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="G634" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="I634" t="s">
-        <v>715</v>
+        <v>1484</v>
       </c>
       <c r="K634" t="s">
-        <v>196</v>
+        <v>620</v>
       </c>
       <c r="N634">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O634" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="P634" t="s">
         <v>30</v>
@@ -43724,66 +43714,13 @@
       <c r="Q634" t="s">
         <v>30</v>
       </c>
-      <c r="R634">
-        <v>9354</v>
-      </c>
       <c r="S634" t="s">
-        <v>1484</v>
+        <v>30</v>
       </c>
       <c r="T634" t="s">
-        <v>2401</v>
+        <v>30</v>
       </c>
       <c r="U634" t="s">
-        <v>2402</v>
-      </c>
-    </row>
-    <row r="635" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A635" s="1">
-        <v>633</v>
-      </c>
-      <c r="B635">
-        <v>633</v>
-      </c>
-      <c r="C635" t="s">
-        <v>950</v>
-      </c>
-      <c r="D635" t="s">
-        <v>1471</v>
-      </c>
-      <c r="E635" t="s">
-        <v>1414</v>
-      </c>
-      <c r="F635" t="s">
-        <v>1485</v>
-      </c>
-      <c r="G635" t="s">
-        <v>800</v>
-      </c>
-      <c r="I635" t="s">
-        <v>1486</v>
-      </c>
-      <c r="K635" t="s">
-        <v>620</v>
-      </c>
-      <c r="N635">
-        <v>324</v>
-      </c>
-      <c r="O635" t="s">
-        <v>30</v>
-      </c>
-      <c r="P635" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q635" t="s">
-        <v>30</v>
-      </c>
-      <c r="S635" t="s">
-        <v>30</v>
-      </c>
-      <c r="T635" t="s">
-        <v>30</v>
-      </c>
-      <c r="U635" t="s">
         <v>30</v>
       </c>
     </row>
